--- a/notebook/env_data_BGC.xlsx
+++ b/notebook/env_data_BGC.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anacl\Desktop\Programa_Corredor_Donas\R Code\python_notebook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BB224AC-B327-45B5-A025-88834DFC309F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB9208F-5CB6-47BD-B8F2-18BDC613CB20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="envdata_template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3547" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3810" uniqueCount="1064">
   <si>
     <t>BIOSAMPLE_ID</t>
   </si>
@@ -2737,9 +2737,6 @@
     <t>on_axis</t>
   </si>
   <si>
-    <t>Sedimentary; Sedimentary: undivided</t>
-  </si>
-  <si>
     <t>ISL21_KR1_210530_F</t>
   </si>
   <si>
@@ -2882,16 +2879,350 @@
   </si>
   <si>
     <t>FEN_VR_S</t>
+  </si>
+  <si>
+    <t>MNG23_SJ_230730_F</t>
+  </si>
+  <si>
+    <t>MNG23</t>
+  </si>
+  <si>
+    <t>SJ</t>
+  </si>
+  <si>
+    <t>SJ_230730</t>
+  </si>
+  <si>
+    <t>Shargaljuut</t>
+  </si>
+  <si>
+    <t>AS</t>
+  </si>
+  <si>
+    <t>Mongolia</t>
+  </si>
+  <si>
+    <t>paleo</t>
+  </si>
+  <si>
+    <t>MNG23_SJ_230730_S</t>
+  </si>
+  <si>
+    <t>MNG23_TR_230731_F</t>
+  </si>
+  <si>
+    <t>MNG23_TR_230731_S</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>TR_230731</t>
+  </si>
+  <si>
+    <t>Taragt</t>
+  </si>
+  <si>
+    <t>NR</t>
+  </si>
+  <si>
+    <t>NR_230731</t>
+  </si>
+  <si>
+    <t>MNG23_NR_230731_S</t>
+  </si>
+  <si>
+    <t>MNG23_NR_230731_F</t>
+  </si>
+  <si>
+    <t>Nariinteel</t>
+  </si>
+  <si>
+    <t>46.128628</t>
+  </si>
+  <si>
+    <t>46.33309</t>
+  </si>
+  <si>
+    <t>46.273908</t>
+  </si>
+  <si>
+    <t>101.605386</t>
+  </si>
+  <si>
+    <t>101.605387</t>
+  </si>
+  <si>
+    <t>101.224945</t>
+  </si>
+  <si>
+    <t>102.473959</t>
+  </si>
+  <si>
+    <t>22.295</t>
+  </si>
+  <si>
+    <t>6.464</t>
+  </si>
+  <si>
+    <t>56.074</t>
+  </si>
+  <si>
+    <t>39.901</t>
+  </si>
+  <si>
+    <t>79.101</t>
+  </si>
+  <si>
+    <t>56.7305</t>
+  </si>
+  <si>
+    <t>92.5405</t>
+  </si>
+  <si>
+    <t>2.026</t>
+  </si>
+  <si>
+    <t>2.702</t>
+  </si>
+  <si>
+    <t>2.0725</t>
+  </si>
+  <si>
+    <t>2.956</t>
+  </si>
+  <si>
+    <t>3.605</t>
+  </si>
+  <si>
+    <t>4.0475</t>
+  </si>
+  <si>
+    <t>36.22333</t>
+  </si>
+  <si>
+    <t>12.605</t>
+  </si>
+  <si>
+    <t>45.375</t>
+  </si>
+  <si>
+    <t>3.210</t>
+  </si>
+  <si>
+    <t>1.624</t>
+  </si>
+  <si>
+    <t>1.324667</t>
+  </si>
+  <si>
+    <t>37.155</t>
+  </si>
+  <si>
+    <t>41.542</t>
+  </si>
+  <si>
+    <t>98.00367</t>
+  </si>
+  <si>
+    <t>20.69833</t>
+  </si>
+  <si>
+    <t>7.005667</t>
+  </si>
+  <si>
+    <t>2.032333</t>
+  </si>
+  <si>
+    <t>41.38033</t>
+  </si>
+  <si>
+    <t>41.38034</t>
+  </si>
+  <si>
+    <t>35.652</t>
+  </si>
+  <si>
+    <t>2.112333</t>
+  </si>
+  <si>
+    <t>KJ</t>
+  </si>
+  <si>
+    <t>MNG23_KJ_230721_F</t>
+  </si>
+  <si>
+    <t>KJ_230721</t>
+  </si>
+  <si>
+    <t>Khujirt</t>
+  </si>
+  <si>
+    <t>46.9019233</t>
+  </si>
+  <si>
+    <t>102.7696788</t>
+  </si>
+  <si>
+    <t>12.094</t>
+  </si>
+  <si>
+    <t>33.0965</t>
+  </si>
+  <si>
+    <t>82.5125</t>
+  </si>
+  <si>
+    <t>3.382</t>
+  </si>
+  <si>
+    <t>3.234</t>
+  </si>
+  <si>
+    <t>49050.531132</t>
+  </si>
+  <si>
+    <t>50734.858144</t>
+  </si>
+  <si>
+    <t>50142.298246</t>
+  </si>
+  <si>
+    <t>49093.532252</t>
+  </si>
+  <si>
+    <t>GUY_SRR21545384</t>
+  </si>
+  <si>
+    <t>GUY</t>
+  </si>
+  <si>
+    <t>SRR</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>GUY_SRR21545382</t>
+  </si>
+  <si>
+    <t>16236.722508</t>
+  </si>
+  <si>
+    <t>16236.722509</t>
+  </si>
+  <si>
+    <t>GUY_SRR21545388</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>EPR_CV74</t>
+  </si>
+  <si>
+    <t>EPR</t>
+  </si>
+  <si>
+    <t>9.8383</t>
+  </si>
+  <si>
+    <t>−104.2883</t>
+  </si>
+  <si>
+    <t>EPR_CV84</t>
+  </si>
+  <si>
+    <t>9.8398</t>
+  </si>
+  <si>
+    <t>−104.2915</t>
+  </si>
+  <si>
+    <t>EPR_CV88</t>
+  </si>
+  <si>
+    <t>−104.2913</t>
+  </si>
+  <si>
+    <t>7439.304692</t>
+  </si>
+  <si>
+    <t>7439.329577</t>
+  </si>
+  <si>
+    <t>7439.32978</t>
+  </si>
+  <si>
+    <t>Sedimentary</t>
+  </si>
+  <si>
+    <t>EPR_mussel</t>
+  </si>
+  <si>
+    <t>mussel</t>
+  </si>
+  <si>
+    <t>EPR_alvinella</t>
+  </si>
+  <si>
+    <t>alvinella</t>
+  </si>
+  <si>
+    <t>EPR_CV79</t>
+  </si>
+  <si>
+    <t>9.8417</t>
+  </si>
+  <si>
+    <t>−104.2918</t>
+  </si>
+  <si>
+    <t>7439.364907</t>
+  </si>
+  <si>
+    <t>EPR_CV67</t>
+  </si>
+  <si>
+    <t>9.8492</t>
+  </si>
+  <si>
+    <t>−104.2932</t>
+  </si>
+  <si>
+    <t>7439.504148</t>
+  </si>
+  <si>
+    <t>EPR_riftia</t>
+  </si>
+  <si>
+    <t>riftia</t>
+  </si>
+  <si>
+    <t>9.8380</t>
+  </si>
+  <si>
+    <t>−104.2912</t>
+  </si>
+  <si>
+    <t>7439.296122</t>
+  </si>
+  <si>
+    <t>EPR_teddybear</t>
+  </si>
+  <si>
+    <t>teddybear</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2903,6 +3234,32 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2913,7 +3270,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2936,19 +3293,64 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard 2" xfId="1" xr:uid="{BF1C60D4-5BDE-47CF-B9D2-6177DE27CCDA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -3248,10 +3650,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:HF219"/>
+  <dimension ref="A1:HF238"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.6640625" customWidth="1"/>
+    <col min="8" max="8" width="22.88671875" customWidth="1"/>
+    <col min="26" max="26" width="10.109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.109375" customWidth="1"/>
+    <col min="72" max="72" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="167" max="167" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="171" max="171" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="172" max="172" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="198" max="198" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:214" x14ac:dyDescent="0.3">
@@ -3330,7 +3740,7 @@
       <c r="Y1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
       <c r="AA1" s="1" t="s">
@@ -3953,7 +4363,7 @@
       <c r="X2" t="s">
         <v>227</v>
       </c>
-      <c r="Z2">
+      <c r="Z2" s="6">
         <v>38.417501999999999</v>
       </c>
       <c r="AA2">
@@ -4087,7 +4497,7 @@
       <c r="X3" t="s">
         <v>227</v>
       </c>
-      <c r="Z3">
+      <c r="Z3" s="6">
         <v>38.416170999999999</v>
       </c>
       <c r="AA3">
@@ -4221,7 +4631,7 @@
       <c r="X4" t="s">
         <v>227</v>
       </c>
-      <c r="Z4">
+      <c r="Z4" s="6">
         <v>38.416704199999998</v>
       </c>
       <c r="AA4">
@@ -4355,7 +4765,7 @@
       <c r="X5" t="s">
         <v>227</v>
       </c>
-      <c r="Z5">
+      <c r="Z5" s="6">
         <v>38.417587099999999</v>
       </c>
       <c r="AA5">
@@ -4471,7 +4881,7 @@
       <c r="X6" t="s">
         <v>227</v>
       </c>
-      <c r="Z6">
+      <c r="Z6" s="6">
         <v>38.412194999999997</v>
       </c>
       <c r="AA6">
@@ -4602,7 +5012,7 @@
       <c r="X7" t="s">
         <v>227</v>
       </c>
-      <c r="Z7">
+      <c r="Z7" s="6">
         <v>38.381399999999999</v>
       </c>
       <c r="AA7">
@@ -4712,7 +5122,7 @@
       <c r="X8" t="s">
         <v>227</v>
       </c>
-      <c r="Z8">
+      <c r="Z8" s="6">
         <v>38.381900000000002</v>
       </c>
       <c r="AA8">
@@ -4828,7 +5238,7 @@
       <c r="X9" t="s">
         <v>227</v>
       </c>
-      <c r="Z9">
+      <c r="Z9" s="6">
         <v>38.637718999999997</v>
       </c>
       <c r="AA9">
@@ -4965,7 +5375,7 @@
       <c r="X10" t="s">
         <v>262</v>
       </c>
-      <c r="Z10">
+      <c r="Z10" s="6">
         <v>38.491391</v>
       </c>
       <c r="AA10">
@@ -5099,7 +5509,7 @@
       <c r="X11" t="s">
         <v>262</v>
       </c>
-      <c r="Z11">
+      <c r="Z11" s="6">
         <v>38.477997999999999</v>
       </c>
       <c r="AA11">
@@ -5239,7 +5649,7 @@
       <c r="X12" t="s">
         <v>227</v>
       </c>
-      <c r="Z12">
+      <c r="Z12" s="6">
         <v>38.798403</v>
       </c>
       <c r="AA12">
@@ -5344,7 +5754,7 @@
         <v>276</v>
       </c>
       <c r="H13" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I13">
         <v>2019</v>
@@ -5376,7 +5786,7 @@
       <c r="X13" t="s">
         <v>280</v>
       </c>
-      <c r="Z13">
+      <c r="Z13" s="6">
         <v>-24.182136</v>
       </c>
       <c r="AA13">
@@ -5586,7 +5996,7 @@
         <v>276</v>
       </c>
       <c r="H14" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I14">
         <v>2019</v>
@@ -5618,7 +6028,7 @@
       <c r="X14" t="s">
         <v>280</v>
       </c>
-      <c r="Z14">
+      <c r="Z14" s="6">
         <v>-24.182136</v>
       </c>
       <c r="AA14">
@@ -5828,7 +6238,7 @@
         <v>276</v>
       </c>
       <c r="H15" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I15">
         <v>2019</v>
@@ -5860,7 +6270,7 @@
       <c r="X15" t="s">
         <v>280</v>
       </c>
-      <c r="Z15">
+      <c r="Z15" s="6">
         <v>-25.743034000000002</v>
       </c>
       <c r="AA15">
@@ -6067,7 +6477,7 @@
         <v>276</v>
       </c>
       <c r="H16" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I16">
         <v>2019</v>
@@ -6099,7 +6509,7 @@
       <c r="X16" t="s">
         <v>280</v>
       </c>
-      <c r="Z16">
+      <c r="Z16" s="6">
         <v>-25.743034000000002</v>
       </c>
       <c r="AA16">
@@ -6306,7 +6716,7 @@
         <v>276</v>
       </c>
       <c r="H17" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I17">
         <v>2019</v>
@@ -6338,7 +6748,7 @@
       <c r="X17" t="s">
         <v>280</v>
       </c>
-      <c r="Z17">
+      <c r="Z17" s="6">
         <v>-25.825416000000001</v>
       </c>
       <c r="AA17">
@@ -6545,7 +6955,7 @@
         <v>276</v>
       </c>
       <c r="H18" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I18">
         <v>2019</v>
@@ -6577,7 +6987,7 @@
       <c r="X18" t="s">
         <v>280</v>
       </c>
-      <c r="Z18">
+      <c r="Z18" s="6">
         <v>-25.825416000000001</v>
       </c>
       <c r="AA18">
@@ -6784,7 +7194,7 @@
         <v>276</v>
       </c>
       <c r="H19" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I19">
         <v>2019</v>
@@ -6816,7 +7226,7 @@
       <c r="X19" t="s">
         <v>280</v>
       </c>
-      <c r="Z19">
+      <c r="Z19" s="6">
         <v>-25.858187999999998</v>
       </c>
       <c r="AA19">
@@ -7023,7 +7433,7 @@
         <v>276</v>
       </c>
       <c r="H20" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I20">
         <v>2019</v>
@@ -7055,7 +7465,7 @@
       <c r="X20" t="s">
         <v>280</v>
       </c>
-      <c r="Z20">
+      <c r="Z20" s="6">
         <v>-25.858187999999998</v>
       </c>
       <c r="AA20">
@@ -7262,7 +7672,7 @@
         <v>276</v>
       </c>
       <c r="H21" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I21">
         <v>2019</v>
@@ -7294,7 +7704,7 @@
       <c r="X21" t="s">
         <v>280</v>
       </c>
-      <c r="Z21">
+      <c r="Z21" s="6">
         <v>-25.858243000000002</v>
       </c>
       <c r="AA21">
@@ -7507,7 +7917,7 @@
         <v>276</v>
       </c>
       <c r="H22" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I22">
         <v>2019</v>
@@ -7539,7 +7949,7 @@
       <c r="X22" t="s">
         <v>280</v>
       </c>
-      <c r="Z22">
+      <c r="Z22" s="6">
         <v>-25.858243000000002</v>
       </c>
       <c r="AA22">
@@ -7752,7 +8162,7 @@
         <v>276</v>
       </c>
       <c r="H23" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I23">
         <v>2019</v>
@@ -7784,7 +8194,7 @@
       <c r="X23" t="s">
         <v>280</v>
       </c>
-      <c r="Z23">
+      <c r="Z23" s="6">
         <v>-24.282129000000001</v>
       </c>
       <c r="AA23">
@@ -7955,7 +8365,7 @@
         <v>276</v>
       </c>
       <c r="H24" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I24">
         <v>2019</v>
@@ -7987,7 +8397,7 @@
       <c r="X24" t="s">
         <v>280</v>
       </c>
-      <c r="Z24">
+      <c r="Z24" s="6">
         <v>-24.282129000000001</v>
       </c>
       <c r="AA24">
@@ -8158,7 +8568,7 @@
         <v>276</v>
       </c>
       <c r="H25" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I25">
         <v>2019</v>
@@ -8190,7 +8600,7 @@
       <c r="X25" t="s">
         <v>280</v>
       </c>
-      <c r="Z25">
+      <c r="Z25" s="6">
         <v>-26.032910999999999</v>
       </c>
       <c r="AA25">
@@ -8400,7 +8810,7 @@
         <v>276</v>
       </c>
       <c r="H26" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I26">
         <v>2019</v>
@@ -8432,7 +8842,7 @@
       <c r="X26" t="s">
         <v>280</v>
       </c>
-      <c r="Z26">
+      <c r="Z26" s="6">
         <v>-26.032910999999999</v>
       </c>
       <c r="AA26">
@@ -8642,7 +9052,7 @@
         <v>276</v>
       </c>
       <c r="H27" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I27">
         <v>2019</v>
@@ -8674,7 +9084,7 @@
       <c r="X27" t="s">
         <v>280</v>
       </c>
-      <c r="Z27">
+      <c r="Z27" s="6">
         <v>-24.364588999999999</v>
       </c>
       <c r="AA27">
@@ -8881,7 +9291,7 @@
         <v>276</v>
       </c>
       <c r="H28" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I28">
         <v>2019</v>
@@ -8913,7 +9323,7 @@
       <c r="X28" t="s">
         <v>280</v>
       </c>
-      <c r="Z28">
+      <c r="Z28" s="6">
         <v>-24.364588999999999</v>
       </c>
       <c r="AA28">
@@ -9120,7 +9530,7 @@
         <v>276</v>
       </c>
       <c r="H29" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I29">
         <v>2019</v>
@@ -9152,7 +9562,7 @@
       <c r="X29" t="s">
         <v>280</v>
       </c>
-      <c r="Z29">
+      <c r="Z29" s="6">
         <v>-24.246687999999999</v>
       </c>
       <c r="AA29">
@@ -9335,7 +9745,7 @@
         <v>276</v>
       </c>
       <c r="H30" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I30">
         <v>2019</v>
@@ -9367,7 +9777,7 @@
       <c r="X30" t="s">
         <v>280</v>
       </c>
-      <c r="Z30">
+      <c r="Z30" s="6">
         <v>-24.246687999999999</v>
       </c>
       <c r="AA30">
@@ -9550,7 +9960,7 @@
         <v>276</v>
       </c>
       <c r="H31" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I31">
         <v>2019</v>
@@ -9582,7 +9992,7 @@
       <c r="X31" t="s">
         <v>330</v>
       </c>
-      <c r="Z31">
+      <c r="Z31" s="6">
         <v>-24.409859999999998</v>
       </c>
       <c r="AA31">
@@ -9750,7 +10160,7 @@
         <v>276</v>
       </c>
       <c r="H32" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I32">
         <v>2019</v>
@@ -9782,7 +10192,7 @@
       <c r="X32" t="s">
         <v>335</v>
       </c>
-      <c r="Z32">
+      <c r="Z32" s="6">
         <v>-25.409859999999998</v>
       </c>
       <c r="AA32">
@@ -9983,7 +10393,7 @@
         <v>276</v>
       </c>
       <c r="H33" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I33">
         <v>2019</v>
@@ -10015,7 +10425,7 @@
       <c r="X33" t="s">
         <v>340</v>
       </c>
-      <c r="Z33">
+      <c r="Z33" s="6">
         <v>-24.18778</v>
       </c>
       <c r="AA33">
@@ -10180,7 +10590,7 @@
         <v>276</v>
       </c>
       <c r="H34" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I34">
         <v>2019</v>
@@ -10212,7 +10622,7 @@
       <c r="X34" t="s">
         <v>340</v>
       </c>
-      <c r="Z34">
+      <c r="Z34" s="6">
         <v>-24.18778</v>
       </c>
       <c r="AA34">
@@ -10377,7 +10787,7 @@
         <v>276</v>
       </c>
       <c r="H35" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="I35">
         <v>2019</v>
@@ -10409,7 +10819,7 @@
       <c r="X35" t="s">
         <v>335</v>
       </c>
-      <c r="Z35">
+      <c r="Z35" s="6">
         <v>-27.112857999999999</v>
       </c>
       <c r="AA35">
@@ -10616,7 +11026,7 @@
         <v>276</v>
       </c>
       <c r="H36" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I36">
         <v>2020</v>
@@ -10648,7 +11058,7 @@
       <c r="X36" t="s">
         <v>352</v>
       </c>
-      <c r="Z36">
+      <c r="Z36" s="6">
         <v>-34.347661000000002</v>
       </c>
       <c r="AA36">
@@ -10834,7 +11244,7 @@
         <v>276</v>
       </c>
       <c r="H37" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I37">
         <v>2020</v>
@@ -10866,7 +11276,7 @@
       <c r="X37" t="s">
         <v>358</v>
       </c>
-      <c r="Z37">
+      <c r="Z37" s="6">
         <v>-34.958936000000001</v>
       </c>
       <c r="AA37">
@@ -11085,7 +11495,7 @@
         <v>276</v>
       </c>
       <c r="H38" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I38">
         <v>2020</v>
@@ -11117,7 +11527,7 @@
       <c r="X38" t="s">
         <v>358</v>
       </c>
-      <c r="Z38">
+      <c r="Z38" s="6">
         <v>-34.958936000000001</v>
       </c>
       <c r="AA38">
@@ -11336,7 +11746,7 @@
         <v>276</v>
       </c>
       <c r="H39" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I39">
         <v>2020</v>
@@ -11368,7 +11778,7 @@
       <c r="X39" t="s">
         <v>364</v>
       </c>
-      <c r="Z39">
+      <c r="Z39" s="6">
         <v>-33.617739999999998</v>
       </c>
       <c r="AA39">
@@ -11569,7 +11979,7 @@
         <v>276</v>
       </c>
       <c r="H40" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I40">
         <v>2020</v>
@@ -11601,7 +12011,7 @@
       <c r="X40" t="s">
         <v>358</v>
       </c>
-      <c r="Z40">
+      <c r="Z40" s="6">
         <v>-33.824022999999997</v>
       </c>
       <c r="AA40">
@@ -11796,7 +12206,7 @@
         <v>276</v>
       </c>
       <c r="H41" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I41">
         <v>2020</v>
@@ -11828,7 +12238,7 @@
       <c r="X41" t="s">
         <v>358</v>
       </c>
-      <c r="Z41">
+      <c r="Z41" s="6">
         <v>-33.824022999999997</v>
       </c>
       <c r="AA41">
@@ -12023,7 +12433,7 @@
         <v>276</v>
       </c>
       <c r="H42" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I42">
         <v>2020</v>
@@ -12055,7 +12465,7 @@
       <c r="X42" t="s">
         <v>376</v>
       </c>
-      <c r="Z42">
+      <c r="Z42" s="6">
         <v>-35.255208000000003</v>
       </c>
       <c r="AA42">
@@ -12208,7 +12618,7 @@
         <v>276</v>
       </c>
       <c r="H43" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I43">
         <v>2020</v>
@@ -12240,7 +12650,7 @@
       <c r="X43" t="s">
         <v>280</v>
       </c>
-      <c r="Z43">
+      <c r="Z43" s="6">
         <v>-35.136766000000001</v>
       </c>
       <c r="AA43">
@@ -12459,7 +12869,7 @@
         <v>276</v>
       </c>
       <c r="H44" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I44">
         <v>2020</v>
@@ -12491,7 +12901,7 @@
       <c r="X44" t="s">
         <v>280</v>
       </c>
-      <c r="Z44">
+      <c r="Z44" s="6">
         <v>-35.136766000000001</v>
       </c>
       <c r="AA44">
@@ -12710,7 +13120,7 @@
         <v>276</v>
       </c>
       <c r="H45" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I45">
         <v>2020</v>
@@ -12742,7 +13152,7 @@
       <c r="X45" t="s">
         <v>280</v>
       </c>
-      <c r="Z45">
+      <c r="Z45" s="6">
         <v>-35.934109999999997</v>
       </c>
       <c r="AA45">
@@ -12967,7 +13377,7 @@
         <v>276</v>
       </c>
       <c r="H46" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I46">
         <v>2020</v>
@@ -12999,7 +13409,7 @@
       <c r="X46" t="s">
         <v>391</v>
       </c>
-      <c r="Z46">
+      <c r="Z46" s="6">
         <v>-35.822954000000003</v>
       </c>
       <c r="AA46">
@@ -13194,7 +13604,7 @@
         <v>276</v>
       </c>
       <c r="H47" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I47">
         <v>2020</v>
@@ -13226,7 +13636,7 @@
       <c r="X47" t="s">
         <v>391</v>
       </c>
-      <c r="Z47">
+      <c r="Z47" s="6">
         <v>-35.822954000000003</v>
       </c>
       <c r="AA47">
@@ -13421,7 +13831,7 @@
         <v>276</v>
       </c>
       <c r="H48" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I48">
         <v>2020</v>
@@ -13453,7 +13863,7 @@
       <c r="X48" t="s">
         <v>335</v>
       </c>
-      <c r="Z48">
+      <c r="Z48" s="6">
         <v>-35.761243</v>
       </c>
       <c r="AA48">
@@ -13651,7 +14061,7 @@
         <v>276</v>
       </c>
       <c r="H49" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I49">
         <v>2020</v>
@@ -13683,7 +14093,7 @@
       <c r="X49" t="s">
         <v>335</v>
       </c>
-      <c r="Z49">
+      <c r="Z49" s="6">
         <v>-35.761243</v>
       </c>
       <c r="AA49">
@@ -13881,7 +14291,7 @@
         <v>276</v>
       </c>
       <c r="H50" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I50">
         <v>2020</v>
@@ -13913,7 +14323,7 @@
       <c r="X50" t="s">
         <v>335</v>
       </c>
-      <c r="Z50">
+      <c r="Z50" s="6">
         <v>-36.292102</v>
       </c>
       <c r="AA50">
@@ -14105,7 +14515,7 @@
         <v>276</v>
       </c>
       <c r="H51" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I51">
         <v>2020</v>
@@ -14137,7 +14547,7 @@
       <c r="X51" t="s">
         <v>352</v>
       </c>
-      <c r="Z51">
+      <c r="Z51" s="6">
         <v>-32.798668999999997</v>
       </c>
       <c r="AA51">
@@ -14317,7 +14727,7 @@
         <v>276</v>
       </c>
       <c r="H52" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I52">
         <v>2020</v>
@@ -14349,7 +14759,7 @@
       <c r="X52" t="s">
         <v>391</v>
       </c>
-      <c r="Z52">
+      <c r="Z52" s="6">
         <v>-32.892097</v>
       </c>
       <c r="AA52">
@@ -14535,7 +14945,7 @@
         <v>276</v>
       </c>
       <c r="H53" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I53">
         <v>2020</v>
@@ -14567,7 +14977,7 @@
       <c r="X53" t="s">
         <v>391</v>
       </c>
-      <c r="Z53">
+      <c r="Z53" s="6">
         <v>-32.892097</v>
       </c>
       <c r="AA53">
@@ -14753,7 +15163,7 @@
         <v>276</v>
       </c>
       <c r="H54" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I54">
         <v>2022</v>
@@ -14776,7 +15186,7 @@
       <c r="P54" t="s">
         <v>224</v>
       </c>
-      <c r="Z54">
+      <c r="Z54" s="6">
         <v>-23.562899999999999</v>
       </c>
       <c r="AA54">
@@ -14980,7 +15390,7 @@
         <v>276</v>
       </c>
       <c r="H55" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I55">
         <v>2022</v>
@@ -15012,7 +15422,7 @@
       <c r="X55" t="s">
         <v>419</v>
       </c>
-      <c r="Z55">
+      <c r="Z55" s="6">
         <v>-23.697849999999999</v>
       </c>
       <c r="AA55">
@@ -15222,7 +15632,7 @@
         <v>276</v>
       </c>
       <c r="H56" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I56">
         <v>2022</v>
@@ -15254,7 +15664,7 @@
       <c r="X56" t="s">
         <v>280</v>
       </c>
-      <c r="Z56">
+      <c r="Z56" s="6">
         <v>-22.417290000000001</v>
       </c>
       <c r="AA56">
@@ -15494,7 +15904,7 @@
         <v>276</v>
       </c>
       <c r="H57" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I57">
         <v>2022</v>
@@ -15526,7 +15936,7 @@
       <c r="X57" t="s">
         <v>280</v>
       </c>
-      <c r="Z57">
+      <c r="Z57" s="6">
         <v>-22.278110000000002</v>
       </c>
       <c r="AA57">
@@ -15766,7 +16176,7 @@
         <v>276</v>
       </c>
       <c r="H58" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I58">
         <v>2022</v>
@@ -15789,7 +16199,7 @@
       <c r="P58" t="s">
         <v>224</v>
       </c>
-      <c r="Z58">
+      <c r="Z58" s="6">
         <v>-23.149149999999999</v>
       </c>
       <c r="AA58">
@@ -16005,7 +16415,7 @@
         <v>276</v>
       </c>
       <c r="H59" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I59">
         <v>2022</v>
@@ -16037,7 +16447,7 @@
       <c r="X59" t="s">
         <v>280</v>
       </c>
-      <c r="Z59">
+      <c r="Z59" s="6">
         <v>-23.14677</v>
       </c>
       <c r="AA59">
@@ -16274,7 +16684,7 @@
         <v>276</v>
       </c>
       <c r="H60" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I60">
         <v>2022</v>
@@ -16306,7 +16716,7 @@
       <c r="X60" t="s">
         <v>280</v>
       </c>
-      <c r="Z60">
+      <c r="Z60" s="6">
         <v>-22.33071</v>
       </c>
       <c r="AA60">
@@ -16519,7 +16929,7 @@
         <v>276</v>
       </c>
       <c r="H61" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I61">
         <v>2022</v>
@@ -16551,7 +16961,7 @@
       <c r="X61" t="s">
         <v>280</v>
       </c>
-      <c r="Z61">
+      <c r="Z61" s="6">
         <v>-22.356960000000001</v>
       </c>
       <c r="AA61">
@@ -16791,7 +17201,7 @@
         <v>276</v>
       </c>
       <c r="H62" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I62">
         <v>2022</v>
@@ -16823,7 +17233,7 @@
       <c r="X62" t="s">
         <v>280</v>
       </c>
-      <c r="Z62">
+      <c r="Z62" s="6">
         <v>-22.065020000000001</v>
       </c>
       <c r="AA62">
@@ -17006,7 +17416,7 @@
         <v>276</v>
       </c>
       <c r="H63" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I63">
         <v>2022</v>
@@ -17038,7 +17448,7 @@
       <c r="X63" t="s">
         <v>280</v>
       </c>
-      <c r="Z63">
+      <c r="Z63" s="6">
         <v>-21.025147</v>
       </c>
       <c r="AA63">
@@ -17248,7 +17658,7 @@
         <v>276</v>
       </c>
       <c r="H64" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I64">
         <v>2022</v>
@@ -17280,7 +17690,7 @@
       <c r="X64" t="s">
         <v>280</v>
       </c>
-      <c r="Z64">
+      <c r="Z64" s="6">
         <v>-22.064990000000002</v>
       </c>
       <c r="AA64">
@@ -17484,7 +17894,7 @@
         <v>276</v>
       </c>
       <c r="H65" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I65">
         <v>2022</v>
@@ -17516,7 +17926,7 @@
       <c r="X65" t="s">
         <v>280</v>
       </c>
-      <c r="Z65">
+      <c r="Z65" s="6">
         <v>-21.687899999999999</v>
       </c>
       <c r="AA65">
@@ -17750,7 +18160,7 @@
         <v>276</v>
       </c>
       <c r="H66" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I66">
         <v>2022</v>
@@ -17782,7 +18192,7 @@
       <c r="X66" t="s">
         <v>280</v>
       </c>
-      <c r="Z66">
+      <c r="Z66" s="6">
         <v>-21.609522999999999</v>
       </c>
       <c r="AA66">
@@ -18001,7 +18411,7 @@
         <v>276</v>
       </c>
       <c r="H67" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I67">
         <v>2022</v>
@@ -18033,7 +18443,7 @@
       <c r="X67" t="s">
         <v>280</v>
       </c>
-      <c r="Z67">
+      <c r="Z67" s="6">
         <v>-20.070419999999999</v>
       </c>
       <c r="AA67">
@@ -18249,7 +18659,7 @@
         <v>276</v>
       </c>
       <c r="H68" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I68">
         <v>2022</v>
@@ -18281,7 +18691,7 @@
       <c r="X68" t="s">
         <v>280</v>
       </c>
-      <c r="Z68">
+      <c r="Z68" s="6">
         <v>-19.885359999999999</v>
       </c>
       <c r="AA68">
@@ -18485,7 +18895,7 @@
         <v>276</v>
       </c>
       <c r="H69" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I69">
         <v>2022</v>
@@ -18517,7 +18927,7 @@
       <c r="X69" t="s">
         <v>280</v>
       </c>
-      <c r="Z69">
+      <c r="Z69" s="6">
         <v>-19.851839999999999</v>
       </c>
       <c r="AA69">
@@ -18736,7 +19146,7 @@
         <v>276</v>
       </c>
       <c r="H70" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I70">
         <v>2022</v>
@@ -18768,7 +19178,7 @@
       <c r="X70" t="s">
         <v>280</v>
       </c>
-      <c r="Z70">
+      <c r="Z70" s="6">
         <v>-20.725885999999999</v>
       </c>
       <c r="AA70">
@@ -18951,7 +19361,7 @@
         <v>276</v>
       </c>
       <c r="H71" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I71">
         <v>2022</v>
@@ -18983,7 +19393,7 @@
       <c r="X71" t="s">
         <v>335</v>
       </c>
-      <c r="Z71">
+      <c r="Z71" s="6">
         <v>-20.540457</v>
       </c>
       <c r="AA71">
@@ -19190,7 +19600,7 @@
         <v>276</v>
       </c>
       <c r="H72" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I72">
         <v>2022</v>
@@ -19222,7 +19632,7 @@
       <c r="X72" t="s">
         <v>280</v>
       </c>
-      <c r="Z72">
+      <c r="Z72" s="6">
         <v>-19.683479999999999</v>
       </c>
       <c r="AA72">
@@ -19426,7 +19836,7 @@
         <v>276</v>
       </c>
       <c r="H73" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I73">
         <v>2022</v>
@@ -19458,7 +19868,7 @@
       <c r="X73" t="s">
         <v>280</v>
       </c>
-      <c r="Z73">
+      <c r="Z73" s="6">
         <v>-19.120840000000001</v>
       </c>
       <c r="AA73">
@@ -19662,7 +20072,7 @@
         <v>276</v>
       </c>
       <c r="H74" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I74">
         <v>2022</v>
@@ -19694,7 +20104,7 @@
       <c r="X74" t="s">
         <v>280</v>
       </c>
-      <c r="Z74">
+      <c r="Z74" s="6">
         <v>-19.235060000000001</v>
       </c>
       <c r="AA74">
@@ -19913,7 +20323,7 @@
         <v>276</v>
       </c>
       <c r="H75" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I75">
         <v>2022</v>
@@ -19945,7 +20355,7 @@
       <c r="X75" t="s">
         <v>280</v>
       </c>
-      <c r="Z75">
+      <c r="Z75" s="6">
         <v>-19.113416999999998</v>
       </c>
       <c r="AA75">
@@ -20155,7 +20565,7 @@
         <v>276</v>
       </c>
       <c r="H76" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I76">
         <v>2022</v>
@@ -20187,7 +20597,7 @@
       <c r="X76" t="s">
         <v>280</v>
       </c>
-      <c r="Z76">
+      <c r="Z76" s="6">
         <v>-19.058789999999998</v>
       </c>
       <c r="AA76">
@@ -20403,7 +20813,7 @@
         <v>276</v>
       </c>
       <c r="H77" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I77">
         <v>2022</v>
@@ -20435,7 +20845,7 @@
       <c r="X77" t="s">
         <v>280</v>
       </c>
-      <c r="Z77">
+      <c r="Z77" s="6">
         <v>-19.851761</v>
       </c>
       <c r="AA77">
@@ -20666,7 +21076,7 @@
         <v>276</v>
       </c>
       <c r="H78" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I78">
         <v>2022</v>
@@ -20698,7 +21108,7 @@
       <c r="X78" t="s">
         <v>280</v>
       </c>
-      <c r="Z78">
+      <c r="Z78" s="6">
         <v>-19.057009000000001</v>
       </c>
       <c r="AA78">
@@ -20908,7 +21318,7 @@
         <v>276</v>
       </c>
       <c r="H79" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I79">
         <v>2022</v>
@@ -20940,7 +21350,7 @@
       <c r="X79" t="s">
         <v>280</v>
       </c>
-      <c r="Z79">
+      <c r="Z79" s="6">
         <v>-19.232990000000001</v>
       </c>
       <c r="AA79">
@@ -21156,7 +21566,7 @@
         <v>276</v>
       </c>
       <c r="H80" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I80">
         <v>2022</v>
@@ -21188,7 +21598,7 @@
       <c r="X80" t="s">
         <v>280</v>
       </c>
-      <c r="Z80">
+      <c r="Z80" s="6">
         <v>-18.91319</v>
       </c>
       <c r="AA80">
@@ -21413,7 +21823,7 @@
         <v>276</v>
       </c>
       <c r="H81" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I81">
         <v>2022</v>
@@ -21445,7 +21855,7 @@
       <c r="X81" t="s">
         <v>280</v>
       </c>
-      <c r="Z81">
+      <c r="Z81" s="6">
         <v>-17.950050000000001</v>
       </c>
       <c r="AA81">
@@ -21661,7 +22071,7 @@
         <v>276</v>
       </c>
       <c r="H82" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I82">
         <v>2022</v>
@@ -21693,7 +22103,7 @@
       <c r="X82" t="s">
         <v>280</v>
       </c>
-      <c r="Z82">
+      <c r="Z82" s="6">
         <v>-17.955539999999999</v>
       </c>
       <c r="AA82">
@@ -21930,7 +22340,7 @@
         <v>276</v>
       </c>
       <c r="H83" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I83">
         <v>2022</v>
@@ -21962,7 +22372,7 @@
       <c r="X83" t="s">
         <v>280</v>
       </c>
-      <c r="Z83">
+      <c r="Z83" s="6">
         <v>-18.169969999999999</v>
       </c>
       <c r="AA83">
@@ -22181,7 +22591,7 @@
         <v>276</v>
       </c>
       <c r="H84" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I84">
         <v>2022</v>
@@ -22213,7 +22623,7 @@
       <c r="X84" t="s">
         <v>280</v>
       </c>
-      <c r="Z84">
+      <c r="Z84" s="6">
         <v>-18.19791</v>
       </c>
       <c r="AA84">
@@ -22426,7 +22836,7 @@
         <v>276</v>
       </c>
       <c r="H85" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I85">
         <v>2022</v>
@@ -22458,7 +22868,7 @@
       <c r="X85" t="s">
         <v>280</v>
       </c>
-      <c r="Z85">
+      <c r="Z85" s="6">
         <v>-18.2102</v>
       </c>
       <c r="AA85">
@@ -22668,7 +23078,7 @@
         <v>541</v>
       </c>
       <c r="H86" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I86">
         <v>2017</v>
@@ -22694,7 +23104,7 @@
         <v>545</v>
       </c>
       <c r="H87" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I87">
         <v>2017</v>
@@ -22726,7 +23136,7 @@
       <c r="X87" t="s">
         <v>546</v>
       </c>
-      <c r="Z87">
+      <c r="Z87" s="6">
         <v>10.810883</v>
       </c>
       <c r="AA87">
@@ -22852,7 +23262,7 @@
         <v>550</v>
       </c>
       <c r="H88" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I88">
         <v>2017</v>
@@ -22884,7 +23294,7 @@
       <c r="X88" t="s">
         <v>546</v>
       </c>
-      <c r="Z88">
+      <c r="Z88" s="6">
         <v>10.89837</v>
       </c>
       <c r="AA88">
@@ -23046,7 +23456,7 @@
         <v>550</v>
       </c>
       <c r="H89" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I89">
         <v>2017</v>
@@ -23078,7 +23488,7 @@
       <c r="X89" t="s">
         <v>546</v>
       </c>
-      <c r="Z89">
+      <c r="Z89" s="6">
         <v>10.89837</v>
       </c>
       <c r="AA89">
@@ -23240,7 +23650,7 @@
         <v>555</v>
       </c>
       <c r="H90" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I90">
         <v>2017</v>
@@ -23272,7 +23682,7 @@
       <c r="X90" t="s">
         <v>546</v>
       </c>
-      <c r="Z90">
+      <c r="Z90" s="6">
         <v>10.89837</v>
       </c>
       <c r="AA90">
@@ -23365,7 +23775,7 @@
         <v>555</v>
       </c>
       <c r="H91" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I91">
         <v>2017</v>
@@ -23397,7 +23807,7 @@
       <c r="X91" t="s">
         <v>546</v>
       </c>
-      <c r="Z91">
+      <c r="Z91" s="6">
         <v>10.89837</v>
       </c>
       <c r="AA91">
@@ -23490,7 +23900,7 @@
         <v>560</v>
       </c>
       <c r="H92" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I92">
         <v>2017</v>
@@ -23522,7 +23932,7 @@
       <c r="X92" t="s">
         <v>335</v>
       </c>
-      <c r="Z92">
+      <c r="Z92" s="6">
         <v>10.287497</v>
       </c>
       <c r="AA92">
@@ -23681,7 +24091,7 @@
         <v>560</v>
       </c>
       <c r="H93" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I93">
         <v>2017</v>
@@ -23713,7 +24123,7 @@
       <c r="X93" t="s">
         <v>335</v>
       </c>
-      <c r="Z93">
+      <c r="Z93" s="6">
         <v>10.287497</v>
       </c>
       <c r="AA93">
@@ -23872,7 +24282,7 @@
         <v>565</v>
       </c>
       <c r="H94" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I94">
         <v>2017</v>
@@ -23904,7 +24314,7 @@
       <c r="X94" t="s">
         <v>567</v>
       </c>
-      <c r="Z94">
+      <c r="Z94" s="6">
         <v>9.901885</v>
       </c>
       <c r="AA94">
@@ -24045,7 +24455,7 @@
         <v>565</v>
       </c>
       <c r="H95" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I95">
         <v>2017</v>
@@ -24077,7 +24487,7 @@
       <c r="X95" t="s">
         <v>567</v>
       </c>
-      <c r="Z95">
+      <c r="Z95" s="6">
         <v>9.901885</v>
       </c>
       <c r="AA95">
@@ -24218,7 +24628,7 @@
         <v>572</v>
       </c>
       <c r="H96" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I96">
         <v>2017</v>
@@ -24250,7 +24660,7 @@
       <c r="X96" t="s">
         <v>567</v>
       </c>
-      <c r="Z96">
+      <c r="Z96" s="6">
         <v>9.8990050000000007</v>
       </c>
       <c r="AA96">
@@ -24322,7 +24732,7 @@
         <v>576</v>
       </c>
       <c r="H97" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I97">
         <v>2017</v>
@@ -24354,7 +24764,7 @@
       <c r="X97" t="s">
         <v>546</v>
       </c>
-      <c r="Z97">
+      <c r="Z97" s="6">
         <v>10.484006000000001</v>
       </c>
       <c r="AA97">
@@ -24444,7 +24854,7 @@
         <v>580</v>
       </c>
       <c r="H98" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I98">
         <v>2017</v>
@@ -24476,7 +24886,7 @@
       <c r="X98" t="s">
         <v>335</v>
       </c>
-      <c r="Z98">
+      <c r="Z98" s="6">
         <v>10.336843</v>
       </c>
       <c r="AA98">
@@ -24620,7 +25030,7 @@
         <v>584</v>
       </c>
       <c r="H99" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I99">
         <v>2017</v>
@@ -24652,7 +25062,7 @@
       <c r="X99" t="s">
         <v>546</v>
       </c>
-      <c r="Z99">
+      <c r="Z99" s="6">
         <v>10.595774</v>
       </c>
       <c r="AA99">
@@ -24814,7 +25224,7 @@
         <v>588</v>
       </c>
       <c r="H100" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I100">
         <v>2017</v>
@@ -24846,7 +25256,7 @@
       <c r="X100" t="s">
         <v>546</v>
       </c>
-      <c r="Z100">
+      <c r="Z100" s="6">
         <v>10.518466</v>
       </c>
       <c r="AA100">
@@ -25002,7 +25412,7 @@
         <v>588</v>
       </c>
       <c r="H101" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I101">
         <v>2017</v>
@@ -25034,7 +25444,7 @@
       <c r="X101" t="s">
         <v>546</v>
       </c>
-      <c r="Z101">
+      <c r="Z101" s="6">
         <v>10.518466</v>
       </c>
       <c r="AA101">
@@ -25190,7 +25600,7 @@
         <v>592</v>
       </c>
       <c r="H102" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I102">
         <v>2017</v>
@@ -25231,7 +25641,7 @@
         <v>592</v>
       </c>
       <c r="H103" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I103">
         <v>2017</v>
@@ -25272,7 +25682,7 @@
         <v>597</v>
       </c>
       <c r="H104" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I104">
         <v>2017</v>
@@ -25304,7 +25714,7 @@
       <c r="X104" t="s">
         <v>546</v>
       </c>
-      <c r="Z104">
+      <c r="Z104" s="6">
         <v>10.196777000000001</v>
       </c>
       <c r="AA104">
@@ -25427,7 +25837,7 @@
         <v>601</v>
       </c>
       <c r="H105" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I105">
         <v>2017</v>
@@ -25459,7 +25869,7 @@
       <c r="X105" t="s">
         <v>602</v>
       </c>
-      <c r="Z105">
+      <c r="Z105" s="6">
         <v>9.5617099999999997</v>
       </c>
       <c r="AA105">
@@ -25567,7 +25977,7 @@
         <v>601</v>
       </c>
       <c r="H106" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I106">
         <v>2017</v>
@@ -25599,7 +26009,7 @@
       <c r="X106" t="s">
         <v>602</v>
       </c>
-      <c r="Z106">
+      <c r="Z106" s="6">
         <v>9.5617099999999997</v>
       </c>
       <c r="AA106">
@@ -25707,7 +26117,7 @@
         <v>601</v>
       </c>
       <c r="H107" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I107">
         <v>2017</v>
@@ -25739,7 +26149,7 @@
       <c r="X107" t="s">
         <v>602</v>
       </c>
-      <c r="Z107">
+      <c r="Z107" s="6">
         <v>9.5615749999999995</v>
       </c>
       <c r="AA107">
@@ -25859,7 +26269,7 @@
         <v>609</v>
       </c>
       <c r="H108" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I108">
         <v>2017</v>
@@ -25891,7 +26301,7 @@
       <c r="X108" t="s">
         <v>546</v>
       </c>
-      <c r="Z108">
+      <c r="Z108" s="6">
         <v>10.495573</v>
       </c>
       <c r="AA108">
@@ -26053,7 +26463,7 @@
         <v>609</v>
       </c>
       <c r="H109" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I109">
         <v>2017</v>
@@ -26085,7 +26495,7 @@
       <c r="X109" t="s">
         <v>546</v>
       </c>
-      <c r="Z109">
+      <c r="Z109" s="6">
         <v>10.495573</v>
       </c>
       <c r="AA109">
@@ -26247,7 +26657,7 @@
         <v>613</v>
       </c>
       <c r="H110" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I110">
         <v>2017</v>
@@ -26279,7 +26689,7 @@
       <c r="X110" t="s">
         <v>615</v>
       </c>
-      <c r="Z110">
+      <c r="Z110" s="6">
         <v>10.232331</v>
       </c>
       <c r="AA110">
@@ -26429,7 +26839,7 @@
         <v>613</v>
       </c>
       <c r="H111" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I111">
         <v>2017</v>
@@ -26461,7 +26871,7 @@
       <c r="X111" t="s">
         <v>615</v>
       </c>
-      <c r="Z111">
+      <c r="Z111" s="6">
         <v>10.232331</v>
       </c>
       <c r="AA111">
@@ -26611,7 +27021,7 @@
         <v>620</v>
       </c>
       <c r="H112" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I112">
         <v>2017</v>
@@ -26643,7 +27053,7 @@
       <c r="X112" t="s">
         <v>546</v>
       </c>
-      <c r="Z112">
+      <c r="Z112" s="6">
         <v>10.321576</v>
       </c>
       <c r="AA112">
@@ -26787,7 +27197,7 @@
         <v>622</v>
       </c>
       <c r="H113" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I113">
         <v>2017</v>
@@ -26876,7 +27286,7 @@
         <v>626</v>
       </c>
       <c r="H114" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I114">
         <v>2017</v>
@@ -26908,7 +27318,7 @@
       <c r="X114" t="s">
         <v>627</v>
       </c>
-      <c r="Z114">
+      <c r="Z114" s="6">
         <v>10.301239000000001</v>
       </c>
       <c r="AA114">
@@ -27025,7 +27435,7 @@
         <v>626</v>
       </c>
       <c r="H115" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I115">
         <v>2017</v>
@@ -27057,7 +27467,7 @@
       <c r="X115" t="s">
         <v>627</v>
       </c>
-      <c r="Z115">
+      <c r="Z115" s="6">
         <v>10.301239000000001</v>
       </c>
       <c r="AA115">
@@ -27174,7 +27584,7 @@
         <v>632</v>
       </c>
       <c r="H116" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I116">
         <v>2017</v>
@@ -27206,7 +27616,7 @@
       <c r="X116" t="s">
         <v>335</v>
       </c>
-      <c r="Z116">
+      <c r="Z116" s="6">
         <v>10.290599</v>
       </c>
       <c r="AA116">
@@ -27323,7 +27733,7 @@
         <v>632</v>
       </c>
       <c r="H117" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I117">
         <v>2017</v>
@@ -27355,7 +27765,7 @@
       <c r="X117" t="s">
         <v>335</v>
       </c>
-      <c r="Z117">
+      <c r="Z117" s="6">
         <v>10.290599</v>
       </c>
       <c r="AA117">
@@ -27472,7 +27882,7 @@
         <v>637</v>
       </c>
       <c r="H118" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I118">
         <v>2017</v>
@@ -27504,7 +27914,7 @@
       <c r="X118" t="s">
         <v>546</v>
       </c>
-      <c r="Z118">
+      <c r="Z118" s="6">
         <v>10.366486</v>
       </c>
       <c r="AA118">
@@ -27666,7 +28076,7 @@
         <v>637</v>
       </c>
       <c r="H119" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I119">
         <v>2017</v>
@@ -27698,7 +28108,7 @@
       <c r="X119" t="s">
         <v>546</v>
       </c>
-      <c r="Z119">
+      <c r="Z119" s="6">
         <v>10.366486</v>
       </c>
       <c r="AA119">
@@ -27860,7 +28270,7 @@
         <v>642</v>
       </c>
       <c r="H120" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I120">
         <v>2018</v>
@@ -27892,7 +28302,7 @@
       <c r="X120" t="s">
         <v>643</v>
       </c>
-      <c r="Z120">
+      <c r="Z120" s="6">
         <v>8.6664499999999993</v>
       </c>
       <c r="AA120">
@@ -27967,7 +28377,7 @@
         <v>647</v>
       </c>
       <c r="H121" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I121">
         <v>2018</v>
@@ -27999,7 +28409,7 @@
       <c r="X121" t="s">
         <v>643</v>
       </c>
-      <c r="Z121">
+      <c r="Z121" s="6">
         <v>8.6658100000000005</v>
       </c>
       <c r="AA121">
@@ -28065,7 +28475,7 @@
         <v>650</v>
       </c>
       <c r="H122" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I122">
         <v>2018</v>
@@ -28097,7 +28507,7 @@
       <c r="X122" t="s">
         <v>643</v>
       </c>
-      <c r="Z122">
+      <c r="Z122" s="6">
         <v>8.7050800000000006</v>
       </c>
       <c r="AA122">
@@ -28208,7 +28618,7 @@
         <v>650</v>
       </c>
       <c r="H123" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I123">
         <v>2018</v>
@@ -28240,7 +28650,7 @@
       <c r="X123" t="s">
         <v>643</v>
       </c>
-      <c r="Z123">
+      <c r="Z123" s="6">
         <v>8.7050800000000006</v>
       </c>
       <c r="AA123">
@@ -28351,7 +28761,7 @@
         <v>655</v>
       </c>
       <c r="H124" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I124">
         <v>2018</v>
@@ -28383,7 +28793,7 @@
       <c r="X124" t="s">
         <v>602</v>
       </c>
-      <c r="Z124">
+      <c r="Z124" s="6">
         <v>7.4410400000000001</v>
       </c>
       <c r="AA124">
@@ -28494,7 +28904,7 @@
         <v>655</v>
       </c>
       <c r="H125" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I125">
         <v>2018</v>
@@ -28526,7 +28936,7 @@
       <c r="X125" t="s">
         <v>602</v>
       </c>
-      <c r="Z125">
+      <c r="Z125" s="6">
         <v>7.4410400000000001</v>
       </c>
       <c r="AA125">
@@ -28637,7 +29047,7 @@
         <v>659</v>
       </c>
       <c r="H126" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I126">
         <v>2018</v>
@@ -28669,7 +29079,7 @@
       <c r="X126" t="s">
         <v>660</v>
       </c>
-      <c r="Z126">
+      <c r="Z126" s="6">
         <v>8.4044799999999995</v>
       </c>
       <c r="AA126">
@@ -28783,7 +29193,7 @@
         <v>664</v>
       </c>
       <c r="H127" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I127">
         <v>2018</v>
@@ -28815,7 +29225,7 @@
       <c r="X127" t="s">
         <v>665</v>
       </c>
-      <c r="Z127">
+      <c r="Z127" s="6">
         <v>8.5991999999999997</v>
       </c>
       <c r="AA127">
@@ -28917,7 +29327,7 @@
         <v>664</v>
       </c>
       <c r="H128" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I128">
         <v>2018</v>
@@ -28949,7 +29359,7 @@
       <c r="X128" t="s">
         <v>665</v>
       </c>
-      <c r="Z128">
+      <c r="Z128" s="6">
         <v>8.5991999999999997</v>
       </c>
       <c r="AA128">
@@ -29051,7 +29461,7 @@
         <v>670</v>
       </c>
       <c r="H129" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I129">
         <v>2018</v>
@@ -29083,7 +29493,7 @@
       <c r="X129" t="s">
         <v>671</v>
       </c>
-      <c r="Z129">
+      <c r="Z129" s="6">
         <v>9.7357460000000007</v>
       </c>
       <c r="AA129">
@@ -29179,7 +29589,7 @@
         <v>670</v>
       </c>
       <c r="H130" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I130">
         <v>2018</v>
@@ -29211,7 +29621,7 @@
       <c r="X130" t="s">
         <v>671</v>
       </c>
-      <c r="Z130">
+      <c r="Z130" s="6">
         <v>9.7357460000000007</v>
       </c>
       <c r="AA130">
@@ -29307,7 +29717,7 @@
         <v>675</v>
       </c>
       <c r="H131" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I131">
         <v>2018</v>
@@ -29339,7 +29749,7 @@
       <c r="X131" t="s">
         <v>643</v>
       </c>
-      <c r="Z131">
+      <c r="Z131" s="6">
         <v>7.7140700000000004</v>
       </c>
       <c r="AA131">
@@ -29432,7 +29842,7 @@
         <v>677</v>
       </c>
       <c r="H132" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I132">
         <v>2018</v>
@@ -29470,7 +29880,7 @@
         <v>681</v>
       </c>
       <c r="H133" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I133">
         <v>2018</v>
@@ -29496,7 +29906,7 @@
       <c r="X133" t="s">
         <v>682</v>
       </c>
-      <c r="Z133">
+      <c r="Z133" s="6">
         <v>9.9382230000000007</v>
       </c>
       <c r="AA133">
@@ -29583,7 +29993,7 @@
         <v>681</v>
       </c>
       <c r="H134" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I134">
         <v>2018</v>
@@ -29609,7 +30019,7 @@
       <c r="X134" t="s">
         <v>682</v>
       </c>
-      <c r="Z134">
+      <c r="Z134" s="6">
         <v>9.9382230000000007</v>
       </c>
       <c r="AA134">
@@ -29696,7 +30106,7 @@
         <v>687</v>
       </c>
       <c r="H135" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I135">
         <v>2018</v>
@@ -29728,7 +30138,7 @@
       <c r="X135" t="s">
         <v>688</v>
       </c>
-      <c r="Z135">
+      <c r="Z135" s="6">
         <v>9.1948333299999998</v>
       </c>
       <c r="AA135">
@@ -29824,7 +30234,7 @@
         <v>692</v>
       </c>
       <c r="H136" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I136">
         <v>2018</v>
@@ -29856,7 +30266,7 @@
       <c r="X136" t="s">
         <v>602</v>
       </c>
-      <c r="Z136">
+      <c r="Z136" s="6">
         <v>9.36022</v>
       </c>
       <c r="AA136">
@@ -29970,7 +30380,7 @@
         <v>696</v>
       </c>
       <c r="H137" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I137">
         <v>2018</v>
@@ -30002,7 +30412,7 @@
       <c r="X137" t="s">
         <v>643</v>
       </c>
-      <c r="Z137">
+      <c r="Z137" s="6">
         <v>8.8073599999999992</v>
       </c>
       <c r="AA137">
@@ -30056,7 +30466,7 @@
         <v>696</v>
       </c>
       <c r="H138" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I138">
         <v>2018</v>
@@ -30088,7 +30498,7 @@
       <c r="X138" t="s">
         <v>643</v>
       </c>
-      <c r="Z138">
+      <c r="Z138" s="6">
         <v>8.8073599999999992</v>
       </c>
       <c r="AA138">
@@ -30142,7 +30552,7 @@
         <v>701</v>
       </c>
       <c r="H139" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I139">
         <v>2018</v>
@@ -30174,7 +30584,7 @@
       <c r="X139" t="s">
         <v>546</v>
       </c>
-      <c r="Z139">
+      <c r="Z139" s="6">
         <v>10.427103000000001</v>
       </c>
       <c r="AA139">
@@ -30231,7 +30641,7 @@
         <v>701</v>
       </c>
       <c r="H140" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I140">
         <v>2018</v>
@@ -30263,7 +30673,7 @@
       <c r="X140" t="s">
         <v>546</v>
       </c>
-      <c r="Z140">
+      <c r="Z140" s="6">
         <v>10.427103000000001</v>
       </c>
       <c r="AA140">
@@ -30320,7 +30730,7 @@
         <v>706</v>
       </c>
       <c r="H141" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I141">
         <v>2018</v>
@@ -30352,7 +30762,7 @@
       <c r="X141" t="s">
         <v>643</v>
       </c>
-      <c r="Z141">
+      <c r="Z141" s="6">
         <v>8.8709500000000006</v>
       </c>
       <c r="AA141">
@@ -30463,7 +30873,7 @@
         <v>706</v>
       </c>
       <c r="H142" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I142">
         <v>2018</v>
@@ -30495,7 +30905,7 @@
       <c r="X142" t="s">
         <v>643</v>
       </c>
-      <c r="Z142">
+      <c r="Z142" s="6">
         <v>8.8709500000000006</v>
       </c>
       <c r="AA142">
@@ -30606,7 +31016,7 @@
         <v>710</v>
       </c>
       <c r="H143" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I143">
         <v>2018</v>
@@ -30638,7 +31048,7 @@
       <c r="X143" t="s">
         <v>643</v>
       </c>
-      <c r="Z143">
+      <c r="Z143" s="6">
         <v>8.8696599999999997</v>
       </c>
       <c r="AA143">
@@ -30749,7 +31159,7 @@
         <v>714</v>
       </c>
       <c r="H144" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I144">
         <v>2018</v>
@@ -30781,7 +31191,7 @@
       <c r="X144" t="s">
         <v>335</v>
       </c>
-      <c r="Z144">
+      <c r="Z144" s="6">
         <v>8.4411900000000006</v>
       </c>
       <c r="AA144">
@@ -30877,7 +31287,7 @@
         <v>714</v>
       </c>
       <c r="H145" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I145">
         <v>2018</v>
@@ -30909,7 +31319,7 @@
       <c r="X145" t="s">
         <v>335</v>
       </c>
-      <c r="Z145">
+      <c r="Z145" s="6">
         <v>8.4411900000000006</v>
       </c>
       <c r="AA145">
@@ -31005,7 +31415,7 @@
         <v>719</v>
       </c>
       <c r="H146" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I146">
         <v>2018</v>
@@ -31037,7 +31447,7 @@
       <c r="X146" t="s">
         <v>688</v>
       </c>
-      <c r="Z146">
+      <c r="Z146" s="6">
         <v>9.3439099999999993</v>
       </c>
       <c r="AA146">
@@ -31136,7 +31546,7 @@
         <v>719</v>
       </c>
       <c r="H147" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I147">
         <v>2018</v>
@@ -31168,7 +31578,7 @@
       <c r="X147" t="s">
         <v>688</v>
       </c>
-      <c r="Z147">
+      <c r="Z147" s="6">
         <v>9.3439099999999993</v>
       </c>
       <c r="AA147">
@@ -31267,7 +31677,7 @@
         <v>724</v>
       </c>
       <c r="H148" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I148">
         <v>2018</v>
@@ -31299,7 +31709,7 @@
       <c r="X148" t="s">
         <v>615</v>
       </c>
-      <c r="Z148">
+      <c r="Z148" s="6">
         <v>8.5755400000000002</v>
       </c>
       <c r="AA148">
@@ -31401,7 +31811,7 @@
         <v>728</v>
       </c>
       <c r="H149" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I149">
         <v>2018</v>
@@ -31433,7 +31843,7 @@
       <c r="X149" t="s">
         <v>546</v>
       </c>
-      <c r="Z149">
+      <c r="Z149" s="6">
         <v>10.488754999999999</v>
       </c>
       <c r="AA149">
@@ -31532,7 +31942,7 @@
         <v>732</v>
       </c>
       <c r="H150" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I150">
         <v>2018</v>
@@ -31564,7 +31974,7 @@
       <c r="X150" t="s">
         <v>733</v>
       </c>
-      <c r="Z150">
+      <c r="Z150" s="6">
         <v>9.3028300000000002</v>
       </c>
       <c r="AA150">
@@ -31648,7 +32058,7 @@
         <v>732</v>
       </c>
       <c r="H151" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I151">
         <v>2018</v>
@@ -31680,7 +32090,7 @@
       <c r="X151" t="s">
         <v>733</v>
       </c>
-      <c r="Z151">
+      <c r="Z151" s="6">
         <v>9.3028300000000002</v>
       </c>
       <c r="AA151">
@@ -31764,7 +32174,7 @@
         <v>738</v>
       </c>
       <c r="H152" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I152">
         <v>2018</v>
@@ -31796,7 +32206,7 @@
       <c r="X152" t="s">
         <v>643</v>
       </c>
-      <c r="Z152">
+      <c r="Z152" s="6">
         <v>8.6359100000000009</v>
       </c>
       <c r="AA152">
@@ -31877,7 +32287,7 @@
         <v>742</v>
       </c>
       <c r="H153" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I153">
         <v>2018</v>
@@ -31909,7 +32319,7 @@
       <c r="X153" t="s">
         <v>660</v>
       </c>
-      <c r="Z153">
+      <c r="Z153" s="6">
         <v>8.1575500000000005</v>
       </c>
       <c r="AA153">
@@ -31981,7 +32391,7 @@
         <v>742</v>
       </c>
       <c r="H154" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I154">
         <v>2018</v>
@@ -32013,7 +32423,7 @@
       <c r="X154" t="s">
         <v>660</v>
       </c>
-      <c r="Z154">
+      <c r="Z154" s="6">
         <v>8.1575500000000005</v>
       </c>
       <c r="AA154">
@@ -32085,7 +32495,7 @@
         <v>747</v>
       </c>
       <c r="H155" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I155">
         <v>2018</v>
@@ -32117,7 +32527,7 @@
       <c r="X155" t="s">
         <v>546</v>
       </c>
-      <c r="Z155">
+      <c r="Z155" s="6">
         <v>10.485523000000001</v>
       </c>
       <c r="AA155">
@@ -32183,7 +32593,7 @@
         <v>747</v>
       </c>
       <c r="H156" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I156">
         <v>2018</v>
@@ -32215,7 +32625,7 @@
       <c r="X156" t="s">
         <v>546</v>
       </c>
-      <c r="Z156">
+      <c r="Z156" s="6">
         <v>10.485523000000001</v>
       </c>
       <c r="AA156">
@@ -32281,7 +32691,7 @@
         <v>752</v>
       </c>
       <c r="H157" t="s">
-        <v>928</v>
+        <v>1031</v>
       </c>
       <c r="I157">
         <v>2018</v>
@@ -32313,7 +32723,7 @@
       <c r="X157" t="s">
         <v>688</v>
       </c>
-      <c r="Z157">
+      <c r="Z157" s="6">
         <v>9.1949199999999998</v>
       </c>
       <c r="AA157">
@@ -32382,7 +32792,7 @@
         <v>6</v>
       </c>
       <c r="H158" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I158">
         <v>2019</v>
@@ -32414,7 +32824,7 @@
       <c r="X158" t="s">
         <v>335</v>
       </c>
-      <c r="Z158">
+      <c r="Z158" s="6">
         <v>10.160508</v>
       </c>
       <c r="AA158">
@@ -32474,7 +32884,7 @@
         <v>6</v>
       </c>
       <c r="H159" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I159">
         <v>2019</v>
@@ -32506,7 +32916,7 @@
       <c r="X159" t="s">
         <v>335</v>
       </c>
-      <c r="Z159">
+      <c r="Z159" s="6">
         <v>10.160508</v>
       </c>
       <c r="AA159">
@@ -32566,7 +32976,7 @@
         <v>17</v>
       </c>
       <c r="H160" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I160">
         <v>2019</v>
@@ -32598,7 +33008,7 @@
       <c r="X160" t="s">
         <v>546</v>
       </c>
-      <c r="Z160">
+      <c r="Z160" s="6">
         <v>10.810506</v>
       </c>
       <c r="AA160">
@@ -32661,7 +33071,7 @@
         <v>12</v>
       </c>
       <c r="H161" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I161">
         <v>2019</v>
@@ -32693,7 +33103,7 @@
       <c r="X161" t="s">
         <v>546</v>
       </c>
-      <c r="Z161">
+      <c r="Z161" s="6">
         <v>10.899661</v>
       </c>
       <c r="AA161">
@@ -32753,7 +33163,7 @@
         <v>7</v>
       </c>
       <c r="H162" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I162">
         <v>2019</v>
@@ -32785,7 +33195,7 @@
       <c r="X162" t="s">
         <v>567</v>
       </c>
-      <c r="Z162">
+      <c r="Z162" s="6">
         <v>9.9020510000000002</v>
       </c>
       <c r="AA162">
@@ -32842,7 +33252,7 @@
         <v>14</v>
       </c>
       <c r="H163" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I163">
         <v>2019</v>
@@ -32874,7 +33284,7 @@
       <c r="X163" t="s">
         <v>546</v>
       </c>
-      <c r="Z163">
+      <c r="Z163" s="6">
         <v>10.483901602175999</v>
       </c>
       <c r="AA163">
@@ -32943,7 +33353,7 @@
         <v>18</v>
       </c>
       <c r="H164" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I164">
         <v>2019</v>
@@ -32975,7 +33385,7 @@
       <c r="X164" t="s">
         <v>280</v>
       </c>
-      <c r="Z164">
+      <c r="Z164" s="6">
         <v>10.756285999999999</v>
       </c>
       <c r="AA164">
@@ -33041,7 +33451,7 @@
         <v>18</v>
       </c>
       <c r="H165" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I165">
         <v>2019</v>
@@ -33073,7 +33483,7 @@
       <c r="X165" t="s">
         <v>280</v>
       </c>
-      <c r="Z165">
+      <c r="Z165" s="6">
         <v>10.756285999999999</v>
       </c>
       <c r="AA165">
@@ -33139,7 +33549,7 @@
         <v>779</v>
       </c>
       <c r="H166" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I166">
         <v>2019</v>
@@ -33171,7 +33581,7 @@
       <c r="X166" t="s">
         <v>546</v>
       </c>
-      <c r="Z166">
+      <c r="Z166" s="6">
         <v>10.088665000000001</v>
       </c>
       <c r="AA166">
@@ -33237,7 +33647,7 @@
         <v>8</v>
       </c>
       <c r="H167" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I167">
         <v>2019</v>
@@ -33269,7 +33679,7 @@
       <c r="X167" t="s">
         <v>546</v>
       </c>
-      <c r="Z167">
+      <c r="Z167" s="6">
         <v>10.77183</v>
       </c>
       <c r="AA167">
@@ -33338,7 +33748,7 @@
         <v>10</v>
       </c>
       <c r="H168" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I168">
         <v>2019</v>
@@ -33370,7 +33780,7 @@
       <c r="X168" t="s">
         <v>546</v>
       </c>
-      <c r="Z168">
+      <c r="Z168" s="6">
         <v>10.003062</v>
       </c>
       <c r="AA168">
@@ -33433,7 +33843,7 @@
         <v>20</v>
       </c>
       <c r="H169" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I169">
         <v>2019</v>
@@ -33462,7 +33872,7 @@
       <c r="X169" t="s">
         <v>546</v>
       </c>
-      <c r="Z169">
+      <c r="Z169" s="6">
         <v>10.355752000000001</v>
       </c>
       <c r="AA169">
@@ -33531,7 +33941,7 @@
         <v>21</v>
       </c>
       <c r="H170" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I170">
         <v>2019</v>
@@ -33560,7 +33970,7 @@
       <c r="X170" t="s">
         <v>546</v>
       </c>
-      <c r="Z170">
+      <c r="Z170" s="6">
         <v>10.355752000000001</v>
       </c>
       <c r="AA170">
@@ -33629,7 +34039,7 @@
         <v>22</v>
       </c>
       <c r="H171" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I171">
         <v>2019</v>
@@ -33658,7 +34068,7 @@
       <c r="X171" t="s">
         <v>546</v>
       </c>
-      <c r="Z171">
+      <c r="Z171" s="6">
         <v>10.355752000000001</v>
       </c>
       <c r="AA171">
@@ -33724,7 +34134,7 @@
         <v>3</v>
       </c>
       <c r="H172" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I172">
         <v>2019</v>
@@ -33753,7 +34163,7 @@
       <c r="X172" t="s">
         <v>546</v>
       </c>
-      <c r="Z172">
+      <c r="Z172" s="6">
         <v>10.355752000000001</v>
       </c>
       <c r="AA172">
@@ -33822,7 +34232,7 @@
         <v>4</v>
       </c>
       <c r="H173" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I173">
         <v>2019</v>
@@ -33851,7 +34261,7 @@
       <c r="X173" t="s">
         <v>546</v>
       </c>
-      <c r="Z173">
+      <c r="Z173" s="6">
         <v>10.355752000000001</v>
       </c>
       <c r="AA173">
@@ -33920,7 +34330,7 @@
         <v>2</v>
       </c>
       <c r="H174" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I174">
         <v>2019</v>
@@ -33952,7 +34362,7 @@
       <c r="X174" t="s">
         <v>546</v>
       </c>
-      <c r="Z174">
+      <c r="Z174" s="6">
         <v>10.3230763722527</v>
       </c>
       <c r="AA174">
@@ -34015,7 +34425,7 @@
         <v>15</v>
       </c>
       <c r="H175" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I175">
         <v>2019</v>
@@ -34038,7 +34448,7 @@
       <c r="P175" t="s">
         <v>224</v>
       </c>
-      <c r="Z175">
+      <c r="Z175" s="6">
         <v>10.86416</v>
       </c>
       <c r="AA175">
@@ -34098,7 +34508,7 @@
         <v>19</v>
       </c>
       <c r="H176" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I176">
         <v>2019</v>
@@ -34130,7 +34540,7 @@
       <c r="X176" t="s">
         <v>546</v>
       </c>
-      <c r="Z176">
+      <c r="Z176" s="6">
         <v>10.5190833732062</v>
       </c>
       <c r="AA176">
@@ -34190,7 +34600,7 @@
         <v>19</v>
       </c>
       <c r="H177" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I177">
         <v>2019</v>
@@ -34222,7 +34632,7 @@
       <c r="X177" t="s">
         <v>546</v>
       </c>
-      <c r="Z177">
+      <c r="Z177" s="6">
         <v>10.5190833732062</v>
       </c>
       <c r="AA177">
@@ -34282,7 +34692,7 @@
         <v>16</v>
       </c>
       <c r="H178" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I178">
         <v>2019</v>
@@ -34314,7 +34724,7 @@
       <c r="X178" t="s">
         <v>280</v>
       </c>
-      <c r="Z178">
+      <c r="Z178" s="6">
         <v>10.803713</v>
       </c>
       <c r="AA178">
@@ -34371,7 +34781,7 @@
         <v>1</v>
       </c>
       <c r="H179" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="I179">
         <v>2019</v>
@@ -34403,7 +34813,7 @@
       <c r="X179" t="s">
         <v>546</v>
       </c>
-      <c r="Z179">
+      <c r="Z179" s="6">
         <v>10.161059</v>
       </c>
       <c r="AA179">
@@ -34427,7 +34837,7 @@
     </row>
     <row r="180" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B180" t="s">
         <v>820</v>
@@ -34456,7 +34866,7 @@
       <c r="J180" s="2">
         <v>44559</v>
       </c>
-      <c r="Z180">
+      <c r="Z180" s="6">
         <v>43.181227999999997</v>
       </c>
       <c r="AA180">
@@ -34477,7 +34887,7 @@
     </row>
     <row r="181" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B181" t="s">
         <v>820</v>
@@ -34506,7 +34916,7 @@
       <c r="J181" s="2">
         <v>44559</v>
       </c>
-      <c r="Z181">
+      <c r="Z181" s="6">
         <v>43.181227999999997</v>
       </c>
       <c r="AA181">
@@ -34527,7 +34937,7 @@
     </row>
     <row r="182" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B182" t="s">
         <v>820</v>
@@ -34583,7 +34993,7 @@
       <c r="Y182" t="s">
         <v>830</v>
       </c>
-      <c r="Z182">
+      <c r="Z182" s="6">
         <v>40.651412000000001</v>
       </c>
       <c r="AA182">
@@ -34697,7 +35107,7 @@
     </row>
     <row r="183" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B183" t="s">
         <v>820</v>
@@ -34753,7 +35163,7 @@
       <c r="Y183" t="s">
         <v>830</v>
       </c>
-      <c r="Z183">
+      <c r="Z183" s="6">
         <v>41.314805999999997</v>
       </c>
       <c r="AA183">
@@ -34867,7 +35277,7 @@
     </row>
     <row r="184" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B184" t="s">
         <v>820</v>
@@ -34923,7 +35333,7 @@
       <c r="Y184" t="s">
         <v>836</v>
       </c>
-      <c r="Z184">
+      <c r="Z184" s="6">
         <v>40.690044999999998</v>
       </c>
       <c r="AA184">
@@ -35049,7 +35459,7 @@
     </row>
     <row r="185" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="B185" t="s">
         <v>820</v>
@@ -35105,7 +35515,7 @@
       <c r="Y185" t="s">
         <v>836</v>
       </c>
-      <c r="Z185">
+      <c r="Z185" s="6">
         <v>40.690044999999998</v>
       </c>
       <c r="AA185">
@@ -35231,7 +35641,7 @@
     </row>
     <row r="186" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B186" t="s">
         <v>820</v>
@@ -35287,7 +35697,7 @@
       <c r="Y186" t="s">
         <v>830</v>
       </c>
-      <c r="Z186">
+      <c r="Z186" s="6">
         <v>40.651556999999997</v>
       </c>
       <c r="AA186">
@@ -35398,7 +35808,7 @@
     </row>
     <row r="187" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B187" t="s">
         <v>820</v>
@@ -35454,7 +35864,7 @@
       <c r="Y187" t="s">
         <v>830</v>
       </c>
-      <c r="Z187">
+      <c r="Z187" s="6">
         <v>40.651556999999997</v>
       </c>
       <c r="AA187">
@@ -35565,7 +35975,7 @@
     </row>
     <row r="188" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B188" t="s">
         <v>820</v>
@@ -35621,7 +36031,7 @@
       <c r="Y188" t="s">
         <v>836</v>
       </c>
-      <c r="Z188">
+      <c r="Z188" s="6">
         <v>40.825108</v>
       </c>
       <c r="AA188">
@@ -35792,7 +36202,7 @@
     </row>
     <row r="189" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B189" t="s">
         <v>820</v>
@@ -35848,7 +36258,7 @@
       <c r="Y189" t="s">
         <v>836</v>
       </c>
-      <c r="Z189">
+      <c r="Z189" s="6">
         <v>40.825108</v>
       </c>
       <c r="AA189">
@@ -36019,7 +36429,7 @@
     </row>
     <row r="190" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B190" t="s">
         <v>820</v>
@@ -36075,7 +36485,7 @@
       <c r="Y190" t="s">
         <v>836</v>
       </c>
-      <c r="Z190">
+      <c r="Z190" s="6">
         <v>40.825380000000003</v>
       </c>
       <c r="AA190">
@@ -36246,7 +36656,7 @@
     </row>
     <row r="191" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B191" t="s">
         <v>820</v>
@@ -36302,7 +36712,7 @@
       <c r="Y191" t="s">
         <v>836</v>
       </c>
-      <c r="Z191">
+      <c r="Z191" s="6">
         <v>40.825380000000003</v>
       </c>
       <c r="AA191">
@@ -36473,7 +36883,7 @@
     </row>
     <row r="192" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B192" t="s">
         <v>820</v>
@@ -36529,7 +36939,7 @@
       <c r="Y192" t="s">
         <v>830</v>
       </c>
-      <c r="Z192">
+      <c r="Z192" s="6">
         <v>41.302894000000002</v>
       </c>
       <c r="AA192">
@@ -36649,7 +37059,7 @@
     </row>
     <row r="193" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="B193" t="s">
         <v>820</v>
@@ -36705,7 +37115,7 @@
       <c r="Y193" t="s">
         <v>851</v>
       </c>
-      <c r="Z193">
+      <c r="Z193" s="6">
         <v>41.314487</v>
       </c>
       <c r="AA193">
@@ -36894,7 +37304,7 @@
     </row>
     <row r="194" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B194" t="s">
         <v>820</v>
@@ -36950,7 +37360,7 @@
       <c r="Y194" t="s">
         <v>851</v>
       </c>
-      <c r="Z194">
+      <c r="Z194" s="6">
         <v>41.314487</v>
       </c>
       <c r="AA194">
@@ -37139,7 +37549,7 @@
     </row>
     <row r="195" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="B195" t="s">
         <v>820</v>
@@ -37195,7 +37605,7 @@
       <c r="Y195" t="s">
         <v>836</v>
       </c>
-      <c r="Z195">
+      <c r="Z195" s="6">
         <v>41.140743000000001</v>
       </c>
       <c r="AA195">
@@ -37366,7 +37776,7 @@
     </row>
     <row r="196" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B196" t="s">
         <v>820</v>
@@ -37422,7 +37832,7 @@
       <c r="Y196" t="s">
         <v>836</v>
       </c>
-      <c r="Z196">
+      <c r="Z196" s="6">
         <v>41.140743000000001</v>
       </c>
       <c r="AA196">
@@ -37593,7 +38003,7 @@
     </row>
     <row r="197" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="B197" t="s">
         <v>820</v>
@@ -37649,7 +38059,7 @@
       <c r="Y197" t="s">
         <v>836</v>
       </c>
-      <c r="Z197">
+      <c r="Z197" s="6">
         <v>41.140756000000003</v>
       </c>
       <c r="AA197">
@@ -37790,7 +38200,7 @@
     </row>
     <row r="198" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B198" t="s">
         <v>820</v>
@@ -37846,7 +38256,7 @@
       <c r="Y198" t="s">
         <v>836</v>
       </c>
-      <c r="Z198">
+      <c r="Z198" s="6">
         <v>41.140756000000003</v>
       </c>
       <c r="AA198">
@@ -37987,7 +38397,7 @@
     </row>
     <row r="199" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B199" t="s">
         <v>820</v>
@@ -38043,7 +38453,7 @@
       <c r="Y199" t="s">
         <v>836</v>
       </c>
-      <c r="Z199">
+      <c r="Z199" s="6">
         <v>40.826908000000003</v>
       </c>
       <c r="AA199">
@@ -38178,7 +38588,7 @@
     </row>
     <row r="200" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B200" t="s">
         <v>820</v>
@@ -38234,7 +38644,7 @@
       <c r="Y200" t="s">
         <v>830</v>
       </c>
-      <c r="Z200">
+      <c r="Z200" s="6">
         <v>41.125095999999999</v>
       </c>
       <c r="AA200">
@@ -38345,7 +38755,7 @@
     </row>
     <row r="201" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B201" t="s">
         <v>820</v>
@@ -38401,7 +38811,7 @@
       <c r="Y201" t="s">
         <v>830</v>
       </c>
-      <c r="Z201">
+      <c r="Z201" s="6">
         <v>41.125095999999999</v>
       </c>
       <c r="AA201">
@@ -38512,7 +38922,7 @@
     </row>
     <row r="202" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B202" t="s">
         <v>820</v>
@@ -38568,7 +38978,7 @@
       <c r="Y202" t="s">
         <v>851</v>
       </c>
-      <c r="Z202">
+      <c r="Z202" s="6">
         <v>40.705666000000001</v>
       </c>
       <c r="AA202">
@@ -38774,7 +39184,7 @@
       <c r="X203" t="s">
         <v>358</v>
       </c>
-      <c r="Z203">
+      <c r="Z203" s="6">
         <v>43.152748600000002</v>
       </c>
       <c r="AA203">
@@ -38962,7 +39372,7 @@
       <c r="X204" t="s">
         <v>358</v>
       </c>
-      <c r="Z204">
+      <c r="Z204" s="6">
         <v>43.167606900000003</v>
       </c>
       <c r="AA204">
@@ -39153,7 +39563,7 @@
       <c r="X205" t="s">
         <v>358</v>
       </c>
-      <c r="Z205">
+      <c r="Z205" s="6">
         <v>43.143527200000001</v>
       </c>
       <c r="AA205">
@@ -39338,7 +39748,7 @@
       <c r="X206" t="s">
         <v>886</v>
       </c>
-      <c r="Z206">
+      <c r="Z206" s="6">
         <v>42.747777999999997</v>
       </c>
       <c r="AA206">
@@ -39526,7 +39936,7 @@
       <c r="X207" t="s">
         <v>886</v>
       </c>
-      <c r="Z207">
+      <c r="Z207" s="6">
         <v>42.504311000000001</v>
       </c>
       <c r="AA207">
@@ -39714,7 +40124,7 @@
       <c r="X208" t="s">
         <v>280</v>
       </c>
-      <c r="Z208">
+      <c r="Z208" s="6">
         <v>42.3984606</v>
       </c>
       <c r="AA208">
@@ -39896,7 +40306,7 @@
       <c r="X209" t="s">
         <v>280</v>
       </c>
-      <c r="Z209">
+      <c r="Z209" s="6">
         <v>41.704585399999999</v>
       </c>
       <c r="AA209">
@@ -40052,7 +40462,7 @@
         <v>219</v>
       </c>
       <c r="H210" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I210">
         <v>2021</v>
@@ -40082,9 +40492,9 @@
         <v>329</v>
       </c>
       <c r="X210" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z210">
+        <v>1044</v>
+      </c>
+      <c r="Z210" s="6">
         <v>63.89546</v>
       </c>
       <c r="AA210">
@@ -40138,7 +40548,7 @@
     </row>
     <row r="211" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B211" t="s">
         <v>899</v>
@@ -40159,7 +40569,7 @@
         <v>219</v>
       </c>
       <c r="H211" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I211">
         <v>2021</v>
@@ -40189,9 +40599,9 @@
         <v>329</v>
       </c>
       <c r="X211" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z211">
+        <v>1044</v>
+      </c>
+      <c r="Z211" s="6">
         <v>63.89546</v>
       </c>
       <c r="AA211">
@@ -40245,16 +40655,16 @@
     </row>
     <row r="212" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B212" t="s">
         <v>899</v>
       </c>
       <c r="C212" t="s">
+        <v>907</v>
+      </c>
+      <c r="D212" t="s">
         <v>908</v>
-      </c>
-      <c r="D212" t="s">
-        <v>909</v>
       </c>
       <c r="E212" t="s">
         <v>902</v>
@@ -40266,7 +40676,7 @@
         <v>219</v>
       </c>
       <c r="H212" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I212">
         <v>2021</v>
@@ -40296,9 +40706,9 @@
         <v>329</v>
       </c>
       <c r="X212" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z212">
+        <v>1044</v>
+      </c>
+      <c r="Z212" s="6">
         <v>63.895451000000001</v>
       </c>
       <c r="AA212">
@@ -40349,16 +40759,16 @@
     </row>
     <row r="213" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B213" t="s">
         <v>899</v>
       </c>
       <c r="C213" t="s">
+        <v>907</v>
+      </c>
+      <c r="D213" t="s">
         <v>908</v>
-      </c>
-      <c r="D213" t="s">
-        <v>909</v>
       </c>
       <c r="E213" t="s">
         <v>902</v>
@@ -40370,7 +40780,7 @@
         <v>219</v>
       </c>
       <c r="H213" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I213">
         <v>2021</v>
@@ -40400,9 +40810,9 @@
         <v>329</v>
       </c>
       <c r="X213" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z213">
+        <v>1044</v>
+      </c>
+      <c r="Z213" s="6">
         <v>63.895451000000001</v>
       </c>
       <c r="AA213">
@@ -40453,19 +40863,19 @@
     </row>
     <row r="214" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B214" t="s">
         <v>899</v>
       </c>
       <c r="C214" t="s">
+        <v>911</v>
+      </c>
+      <c r="D214" t="s">
         <v>912</v>
       </c>
-      <c r="D214" t="s">
+      <c r="E214" t="s">
         <v>913</v>
-      </c>
-      <c r="E214" t="s">
-        <v>914</v>
       </c>
       <c r="F214">
         <v>5</v>
@@ -40474,7 +40884,7 @@
         <v>219</v>
       </c>
       <c r="H214" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I214">
         <v>2021</v>
@@ -40504,9 +40914,9 @@
         <v>329</v>
       </c>
       <c r="X214" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z214">
+        <v>1044</v>
+      </c>
+      <c r="Z214" s="6">
         <v>63.819344000000001</v>
       </c>
       <c r="AA214">
@@ -40563,19 +40973,19 @@
     </row>
     <row r="215" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B215" t="s">
         <v>899</v>
       </c>
       <c r="C215" t="s">
+        <v>915</v>
+      </c>
+      <c r="D215" t="s">
         <v>916</v>
       </c>
-      <c r="D215" t="s">
-        <v>917</v>
-      </c>
       <c r="E215" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F215">
         <v>6</v>
@@ -40584,7 +40994,7 @@
         <v>219</v>
       </c>
       <c r="H215" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I215">
         <v>2021</v>
@@ -40614,9 +41024,9 @@
         <v>329</v>
       </c>
       <c r="X215" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z215">
+        <v>1044</v>
+      </c>
+      <c r="Z215" s="6">
         <v>63.819333999999998</v>
       </c>
       <c r="AA215">
@@ -40670,19 +41080,19 @@
     </row>
     <row r="216" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B216" t="s">
         <v>899</v>
       </c>
       <c r="C216" t="s">
+        <v>918</v>
+      </c>
+      <c r="D216" t="s">
         <v>919</v>
       </c>
-      <c r="D216" t="s">
+      <c r="E216" t="s">
         <v>920</v>
-      </c>
-      <c r="E216" t="s">
-        <v>921</v>
       </c>
       <c r="F216">
         <v>7</v>
@@ -40691,7 +41101,7 @@
         <v>219</v>
       </c>
       <c r="H216" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I216">
         <v>2021</v>
@@ -40721,9 +41131,9 @@
         <v>329</v>
       </c>
       <c r="X216" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z216">
+        <v>1044</v>
+      </c>
+      <c r="Z216" s="6">
         <v>64.008116999999999</v>
       </c>
       <c r="AA216">
@@ -40774,19 +41184,19 @@
     </row>
     <row r="217" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B217" t="s">
         <v>899</v>
       </c>
       <c r="C217" t="s">
+        <v>918</v>
+      </c>
+      <c r="D217" t="s">
         <v>919</v>
       </c>
-      <c r="D217" t="s">
+      <c r="E217" t="s">
         <v>920</v>
-      </c>
-      <c r="E217" t="s">
-        <v>921</v>
       </c>
       <c r="F217">
         <v>7</v>
@@ -40795,7 +41205,7 @@
         <v>219</v>
       </c>
       <c r="H217" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I217">
         <v>2021</v>
@@ -40825,9 +41235,9 @@
         <v>329</v>
       </c>
       <c r="X217" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z217">
+        <v>1044</v>
+      </c>
+      <c r="Z217" s="6">
         <v>64.008116999999999</v>
       </c>
       <c r="AA217">
@@ -40878,19 +41288,19 @@
     </row>
     <row r="218" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B218" t="s">
         <v>899</v>
       </c>
       <c r="C218" t="s">
+        <v>923</v>
+      </c>
+      <c r="D218" t="s">
         <v>924</v>
       </c>
-      <c r="D218" t="s">
-        <v>925</v>
-      </c>
       <c r="E218" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F218">
         <v>8</v>
@@ -40899,7 +41309,7 @@
         <v>219</v>
       </c>
       <c r="H218" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I218">
         <v>2021</v>
@@ -40929,9 +41339,9 @@
         <v>329</v>
       </c>
       <c r="X218" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z218">
+        <v>1044</v>
+      </c>
+      <c r="Z218" s="6">
         <v>64.007062000000005</v>
       </c>
       <c r="AA218">
@@ -40982,19 +41392,19 @@
     </row>
     <row r="219" spans="1:198" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B219" t="s">
         <v>899</v>
       </c>
       <c r="C219" t="s">
+        <v>923</v>
+      </c>
+      <c r="D219" t="s">
         <v>924</v>
       </c>
-      <c r="D219" t="s">
-        <v>925</v>
-      </c>
       <c r="E219" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F219">
         <v>8</v>
@@ -41003,7 +41413,7 @@
         <v>219</v>
       </c>
       <c r="H219" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="I219">
         <v>2021</v>
@@ -41033,9 +41443,9 @@
         <v>329</v>
       </c>
       <c r="X219" t="s">
-        <v>905</v>
-      </c>
-      <c r="Z219">
+        <v>1044</v>
+      </c>
+      <c r="Z219" s="6">
         <v>64.007062000000005</v>
       </c>
       <c r="AA219">
@@ -41084,7 +41494,1640 @@
         <v>20197.044946999999</v>
       </c>
     </row>
+    <row r="220" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A220" t="s">
+        <v>962</v>
+      </c>
+      <c r="B220" t="s">
+        <v>954</v>
+      </c>
+      <c r="C220" t="s">
+        <v>964</v>
+      </c>
+      <c r="D220" t="s">
+        <v>965</v>
+      </c>
+      <c r="E220" t="s">
+        <v>966</v>
+      </c>
+      <c r="G220" t="s">
+        <v>958</v>
+      </c>
+      <c r="H220" t="s">
+        <v>959</v>
+      </c>
+      <c r="I220">
+        <v>2023</v>
+      </c>
+      <c r="L220" t="s">
+        <v>873</v>
+      </c>
+      <c r="M220" t="s">
+        <v>873</v>
+      </c>
+      <c r="N220" t="s">
+        <v>874</v>
+      </c>
+      <c r="O220" t="s">
+        <v>960</v>
+      </c>
+      <c r="P220" t="s">
+        <v>224</v>
+      </c>
+      <c r="V220" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z220" s="6" t="s">
+        <v>974</v>
+      </c>
+      <c r="AA220" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="AB220">
+        <v>1946.1</v>
+      </c>
+      <c r="AC220">
+        <v>52.4</v>
+      </c>
+      <c r="AD220">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="AE220">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="AF220">
+        <v>-76.900000000000006</v>
+      </c>
+      <c r="AG220">
+        <v>42.4</v>
+      </c>
+      <c r="AH220">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AI220">
+        <v>378</v>
+      </c>
+      <c r="AJ220">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AK220">
+        <v>287.87</v>
+      </c>
+      <c r="AM220">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="AN220">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AS220">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AU220">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="AV220" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="AX220">
+        <v>0.38250000000000001</v>
+      </c>
+      <c r="AY220">
+        <v>84.62</v>
+      </c>
+      <c r="AZ220">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="BA220" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="BC220" s="6" t="s">
+        <v>989</v>
+      </c>
+      <c r="BD220">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="BE220" s="6" t="s">
+        <v>995</v>
+      </c>
+      <c r="BF220" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="BG220" s="3"/>
+      <c r="BH220" s="3"/>
+      <c r="BI220" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="BJ220" s="3"/>
+      <c r="BK220" s="3"/>
+      <c r="BL220" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="BN220">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="BR220">
+        <v>4.43</v>
+      </c>
+      <c r="BS220" s="3">
+        <v>8966</v>
+      </c>
+      <c r="BT220">
+        <v>29.96</v>
+      </c>
+      <c r="BU220">
+        <v>32.93</v>
+      </c>
+      <c r="BV220">
+        <v>56.42</v>
+      </c>
+      <c r="CB220">
+        <v>82.39</v>
+      </c>
+      <c r="CC220">
+        <v>6.98</v>
+      </c>
+      <c r="CS220">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="EX220">
+        <v>-12.24</v>
+      </c>
+      <c r="FJ220">
+        <v>0.16807911934596401</v>
+      </c>
+      <c r="FK220" s="3">
+        <v>1430</v>
+      </c>
+      <c r="FL220">
+        <v>0</v>
+      </c>
+      <c r="FM220" s="4">
+        <v>0.96159843639999998</v>
+      </c>
+      <c r="FN220">
+        <v>0</v>
+      </c>
+      <c r="FO220" s="3">
+        <v>7308</v>
+      </c>
+      <c r="FP220" s="3">
+        <v>13417</v>
+      </c>
+      <c r="FQ220" s="3">
+        <v>976713</v>
+      </c>
+      <c r="FR220" s="3">
+        <v>0</v>
+      </c>
+      <c r="FU220" s="3">
+        <v>4253</v>
+      </c>
+      <c r="FV220" s="3">
+        <v>36207</v>
+      </c>
+      <c r="FX220" s="3">
+        <v>24332</v>
+      </c>
+      <c r="FZ220" s="3">
+        <v>184941</v>
+      </c>
+      <c r="GA220">
+        <v>339.51</v>
+      </c>
+      <c r="GB220" s="3"/>
+      <c r="GP220" s="6" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="221" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A221" t="s">
+        <v>963</v>
+      </c>
+      <c r="B221" t="s">
+        <v>954</v>
+      </c>
+      <c r="C221" t="s">
+        <v>964</v>
+      </c>
+      <c r="D221" t="s">
+        <v>965</v>
+      </c>
+      <c r="E221" t="s">
+        <v>966</v>
+      </c>
+      <c r="G221" t="s">
+        <v>958</v>
+      </c>
+      <c r="H221" t="s">
+        <v>959</v>
+      </c>
+      <c r="I221">
+        <v>2023</v>
+      </c>
+      <c r="L221" t="s">
+        <v>873</v>
+      </c>
+      <c r="M221" t="s">
+        <v>873</v>
+      </c>
+      <c r="N221" t="s">
+        <v>874</v>
+      </c>
+      <c r="O221" t="s">
+        <v>960</v>
+      </c>
+      <c r="P221" t="s">
+        <v>224</v>
+      </c>
+      <c r="V221" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z221" s="6" t="s">
+        <v>974</v>
+      </c>
+      <c r="AA221" s="6" t="s">
+        <v>978</v>
+      </c>
+      <c r="AB221">
+        <v>1946.1</v>
+      </c>
+      <c r="AC221">
+        <v>52.4</v>
+      </c>
+      <c r="AD221">
+        <v>9.5500000000000007</v>
+      </c>
+      <c r="AE221">
+        <v>0.78300000000000003</v>
+      </c>
+      <c r="AF221">
+        <v>-76.900000000000006</v>
+      </c>
+      <c r="AG221">
+        <v>42.4</v>
+      </c>
+      <c r="AH221">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="AI221">
+        <v>378</v>
+      </c>
+      <c r="AJ221">
+        <v>3.5999999999999997E-2</v>
+      </c>
+      <c r="AK221">
+        <v>287.87</v>
+      </c>
+      <c r="AM221">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="AN221">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="AS221">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="AU221">
+        <v>5.8000000000000003E-2</v>
+      </c>
+      <c r="AV221" s="6" t="s">
+        <v>982</v>
+      </c>
+      <c r="AX221">
+        <v>0.38250000000000001</v>
+      </c>
+      <c r="AY221">
+        <v>84.62</v>
+      </c>
+      <c r="AZ221">
+        <v>0.13500000000000001</v>
+      </c>
+      <c r="BA221" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="BC221" s="6" t="s">
+        <v>989</v>
+      </c>
+      <c r="BD221">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="BE221" s="6" t="s">
+        <v>995</v>
+      </c>
+      <c r="BF221" s="6" t="s">
+        <v>994</v>
+      </c>
+      <c r="BG221" s="3"/>
+      <c r="BH221" s="3"/>
+      <c r="BI221" s="6" t="s">
+        <v>996</v>
+      </c>
+      <c r="BJ221" s="3"/>
+      <c r="BK221" s="3"/>
+      <c r="BL221" s="6" t="s">
+        <v>998</v>
+      </c>
+      <c r="BN221">
+        <v>5.2999999999999999E-2</v>
+      </c>
+      <c r="BR221">
+        <v>4.43</v>
+      </c>
+      <c r="BS221" s="3">
+        <v>8966</v>
+      </c>
+      <c r="BT221">
+        <v>29.96</v>
+      </c>
+      <c r="BU221">
+        <v>32.93</v>
+      </c>
+      <c r="BV221">
+        <v>56.42</v>
+      </c>
+      <c r="CB221">
+        <v>82.39</v>
+      </c>
+      <c r="CC221">
+        <v>6.98</v>
+      </c>
+      <c r="CS221">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="EX221">
+        <v>-12.24</v>
+      </c>
+      <c r="FJ221">
+        <v>0.16807911934596401</v>
+      </c>
+      <c r="FK221" s="3">
+        <v>1430</v>
+      </c>
+      <c r="FL221">
+        <v>0</v>
+      </c>
+      <c r="FM221" s="4">
+        <v>0.96159843639999998</v>
+      </c>
+      <c r="FN221">
+        <v>0</v>
+      </c>
+      <c r="FO221" s="3">
+        <v>7308</v>
+      </c>
+      <c r="FP221" s="3">
+        <v>13417</v>
+      </c>
+      <c r="FQ221" s="3">
+        <v>976713</v>
+      </c>
+      <c r="FR221" s="3">
+        <v>0</v>
+      </c>
+      <c r="FU221" s="3">
+        <v>4253</v>
+      </c>
+      <c r="FV221" s="3">
+        <v>36207</v>
+      </c>
+      <c r="FX221" s="3">
+        <v>24332</v>
+      </c>
+      <c r="FZ221" s="3">
+        <v>184941</v>
+      </c>
+      <c r="GA221">
+        <v>339.51</v>
+      </c>
+      <c r="GP221" s="6" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="222" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A222" t="s">
+        <v>953</v>
+      </c>
+      <c r="B222" t="s">
+        <v>954</v>
+      </c>
+      <c r="C222" t="s">
+        <v>955</v>
+      </c>
+      <c r="D222" t="s">
+        <v>956</v>
+      </c>
+      <c r="E222" t="s">
+        <v>957</v>
+      </c>
+      <c r="G222" t="s">
+        <v>958</v>
+      </c>
+      <c r="H222" t="s">
+        <v>959</v>
+      </c>
+      <c r="I222">
+        <v>2023</v>
+      </c>
+      <c r="L222" t="s">
+        <v>873</v>
+      </c>
+      <c r="M222" t="s">
+        <v>873</v>
+      </c>
+      <c r="N222" t="s">
+        <v>874</v>
+      </c>
+      <c r="O222" t="s">
+        <v>960</v>
+      </c>
+      <c r="P222" t="s">
+        <v>224</v>
+      </c>
+      <c r="V222" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z222" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="AA222" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="AB222">
+        <v>2151</v>
+      </c>
+      <c r="AC222">
+        <v>88.1</v>
+      </c>
+      <c r="AD222">
+        <v>8.74</v>
+      </c>
+      <c r="AE222">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="AF222">
+        <v>-42.9</v>
+      </c>
+      <c r="AG222">
+        <v>10.6</v>
+      </c>
+      <c r="AH222">
+        <v>0.38</v>
+      </c>
+      <c r="AI222">
+        <v>273</v>
+      </c>
+      <c r="AJ222">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="AK222">
+        <v>240</v>
+      </c>
+      <c r="AM222">
+        <v>0.31</v>
+      </c>
+      <c r="AN222">
+        <v>0</v>
+      </c>
+      <c r="AS222" s="6" t="s">
+        <v>980</v>
+      </c>
+      <c r="AV222" s="6" t="s">
+        <v>981</v>
+      </c>
+      <c r="AX222">
+        <v>0.317</v>
+      </c>
+      <c r="AY222" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="BA222" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="BC222" s="6" t="s">
+        <v>990</v>
+      </c>
+      <c r="BD222">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="BE222" s="6"/>
+      <c r="BF222" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="BI222" s="6">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="BL222" s="6">
+        <v>57.9</v>
+      </c>
+      <c r="BM222">
+        <v>89.56</v>
+      </c>
+      <c r="BP222">
+        <v>99.07</v>
+      </c>
+      <c r="BS222">
+        <v>10.3</v>
+      </c>
+      <c r="BT222">
+        <v>3.98</v>
+      </c>
+      <c r="BU222">
+        <v>62.57</v>
+      </c>
+      <c r="BV222">
+        <v>87.91</v>
+      </c>
+      <c r="CB222">
+        <v>51.86</v>
+      </c>
+      <c r="CC222">
+        <v>7.71</v>
+      </c>
+      <c r="CP222">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="CR222">
+        <v>0.189</v>
+      </c>
+      <c r="CS222">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="EX222">
+        <v>-14.07</v>
+      </c>
+      <c r="FJ222">
+        <v>0</v>
+      </c>
+      <c r="FK222" s="4">
+        <v>0.1418264585</v>
+      </c>
+      <c r="FL222">
+        <v>0</v>
+      </c>
+      <c r="FM222" s="4">
+        <v>0.1643291254</v>
+      </c>
+      <c r="FN222">
+        <v>0</v>
+      </c>
+      <c r="FO222" s="3">
+        <v>154908</v>
+      </c>
+      <c r="FP222" s="3">
+        <v>13623</v>
+      </c>
+      <c r="FQ222" s="3">
+        <v>831162</v>
+      </c>
+      <c r="FR222" s="3">
+        <v>0</v>
+      </c>
+      <c r="FU222" s="3">
+        <v>0</v>
+      </c>
+      <c r="FV222" s="4">
+        <v>1.2048334440000001E-4</v>
+      </c>
+      <c r="FX222" s="4">
+        <v>1.395996404E-4</v>
+      </c>
+      <c r="FZ222" s="4">
+        <v>0.13159639479999999</v>
+      </c>
+      <c r="GA222" s="4">
+        <v>1.157345152E-2</v>
+      </c>
+      <c r="GP222" s="6" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="223" spans="1:198" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A223" t="s">
+        <v>961</v>
+      </c>
+      <c r="B223" t="s">
+        <v>954</v>
+      </c>
+      <c r="C223" t="s">
+        <v>955</v>
+      </c>
+      <c r="D223" t="s">
+        <v>956</v>
+      </c>
+      <c r="E223" t="s">
+        <v>957</v>
+      </c>
+      <c r="G223" t="s">
+        <v>958</v>
+      </c>
+      <c r="H223" t="s">
+        <v>959</v>
+      </c>
+      <c r="I223">
+        <v>2023</v>
+      </c>
+      <c r="L223" t="s">
+        <v>873</v>
+      </c>
+      <c r="M223" t="s">
+        <v>873</v>
+      </c>
+      <c r="N223" t="s">
+        <v>874</v>
+      </c>
+      <c r="O223" t="s">
+        <v>960</v>
+      </c>
+      <c r="P223" t="s">
+        <v>224</v>
+      </c>
+      <c r="V223" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z223" s="6" t="s">
+        <v>973</v>
+      </c>
+      <c r="AA223" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="AB223">
+        <v>2151</v>
+      </c>
+      <c r="AC223">
+        <v>88.1</v>
+      </c>
+      <c r="AD223">
+        <v>8.74</v>
+      </c>
+      <c r="AE223">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="AF223">
+        <v>-42.9</v>
+      </c>
+      <c r="AG223">
+        <v>10.6</v>
+      </c>
+      <c r="AH223">
+        <v>0.38</v>
+      </c>
+      <c r="AI223">
+        <v>273</v>
+      </c>
+      <c r="AJ223">
+        <v>2.6499999999999999E-2</v>
+      </c>
+      <c r="AK223">
+        <v>240</v>
+      </c>
+      <c r="AM223">
+        <v>0.31</v>
+      </c>
+      <c r="AN223">
+        <v>0</v>
+      </c>
+      <c r="AS223" s="6" t="s">
+        <v>980</v>
+      </c>
+      <c r="AV223" s="6" t="s">
+        <v>981</v>
+      </c>
+      <c r="AX223">
+        <v>0.317</v>
+      </c>
+      <c r="AY223" s="6" t="s">
+        <v>983</v>
+      </c>
+      <c r="BA223" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="BC223" s="6" t="s">
+        <v>990</v>
+      </c>
+      <c r="BD223">
+        <v>0.19900000000000001</v>
+      </c>
+      <c r="BE223" s="6"/>
+      <c r="BF223" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="BI223" s="6">
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="BL223" s="6">
+        <v>57.9</v>
+      </c>
+      <c r="BM223">
+        <v>89.56</v>
+      </c>
+      <c r="BP223">
+        <v>99.07</v>
+      </c>
+      <c r="BS223">
+        <v>10.3</v>
+      </c>
+      <c r="BT223">
+        <v>3.98</v>
+      </c>
+      <c r="BU223">
+        <v>62.57</v>
+      </c>
+      <c r="BV223">
+        <v>87.91</v>
+      </c>
+      <c r="CB223">
+        <v>51.86</v>
+      </c>
+      <c r="CC223">
+        <v>7.71</v>
+      </c>
+      <c r="CP223">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="CR223">
+        <v>0.189</v>
+      </c>
+      <c r="CS223">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="EX223">
+        <v>-14.07</v>
+      </c>
+      <c r="FJ223">
+        <v>0</v>
+      </c>
+      <c r="FK223" s="4">
+        <v>0.1418264585</v>
+      </c>
+      <c r="FL223">
+        <v>0</v>
+      </c>
+      <c r="FM223" s="4">
+        <v>0.1643291254</v>
+      </c>
+      <c r="FN223">
+        <v>0</v>
+      </c>
+      <c r="FO223" s="3">
+        <v>154908</v>
+      </c>
+      <c r="FP223" s="3">
+        <v>13623</v>
+      </c>
+      <c r="FQ223" s="3">
+        <v>831162</v>
+      </c>
+      <c r="FR223" s="3">
+        <v>0</v>
+      </c>
+      <c r="FU223" s="3">
+        <v>0</v>
+      </c>
+      <c r="FV223" s="4">
+        <v>1.2048334440000001E-4</v>
+      </c>
+      <c r="FX223" s="4">
+        <v>1.395996404E-4</v>
+      </c>
+      <c r="FZ223" s="4">
+        <v>0.13159639479999999</v>
+      </c>
+      <c r="GA223" s="4">
+        <v>1.157345152E-2</v>
+      </c>
+      <c r="GP223" s="6" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="224" spans="1:198" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A224" t="s">
+        <v>969</v>
+      </c>
+      <c r="B224" t="s">
+        <v>954</v>
+      </c>
+      <c r="C224" t="s">
+        <v>967</v>
+      </c>
+      <c r="D224" t="s">
+        <v>968</v>
+      </c>
+      <c r="E224" t="s">
+        <v>971</v>
+      </c>
+      <c r="G224" t="s">
+        <v>958</v>
+      </c>
+      <c r="H224" t="s">
+        <v>959</v>
+      </c>
+      <c r="I224">
+        <v>2023</v>
+      </c>
+      <c r="L224" t="s">
+        <v>873</v>
+      </c>
+      <c r="M224" t="s">
+        <v>873</v>
+      </c>
+      <c r="N224" t="s">
+        <v>874</v>
+      </c>
+      <c r="O224" t="s">
+        <v>960</v>
+      </c>
+      <c r="P224" t="s">
+        <v>224</v>
+      </c>
+      <c r="V224" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z224" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="AA224" s="7" t="s">
+        <v>975</v>
+      </c>
+      <c r="AB224" s="4">
+        <v>1958.5</v>
+      </c>
+      <c r="AC224" s="8">
+        <v>54.8</v>
+      </c>
+      <c r="AD224" s="8">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="AE224" s="8">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="AF224" s="8">
+        <v>-48.7</v>
+      </c>
+      <c r="AG224" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AH224" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="AI224" s="8">
+        <v>130</v>
+      </c>
+      <c r="AJ224" s="8">
+        <v>1.26E-2</v>
+      </c>
+      <c r="AK224" s="8">
+        <v>210</v>
+      </c>
+      <c r="AL224" s="9"/>
+      <c r="AM224" s="8">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="AN224" s="8">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AS224" s="11" t="s">
+        <v>979</v>
+      </c>
+      <c r="AT224" s="9"/>
+      <c r="AU224" s="8">
+        <v>0.104</v>
+      </c>
+      <c r="AV224" s="11" t="s">
+        <v>984</v>
+      </c>
+      <c r="AW224" s="9"/>
+      <c r="AX224" s="10">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="AY224" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="AZ224" s="9"/>
+      <c r="BA224" s="11" t="s">
+        <v>988</v>
+      </c>
+      <c r="BB224" s="9"/>
+      <c r="BC224" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="BE224" s="6"/>
+      <c r="BF224" s="6" t="s">
+        <v>992</v>
+      </c>
+      <c r="BI224" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="BK224">
+        <v>0.87366699999999997</v>
+      </c>
+      <c r="BL224" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="BM224" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="BP224" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="BS224" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="BT224" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="BU224" s="6" t="s">
+        <v>1004</v>
+      </c>
+      <c r="BX224">
+        <v>0.71033299999999999</v>
+      </c>
+      <c r="CB224" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="CC224" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="GP224" s="6" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="225" spans="1:198" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A225" t="s">
+        <v>970</v>
+      </c>
+      <c r="B225" t="s">
+        <v>954</v>
+      </c>
+      <c r="C225" t="s">
+        <v>967</v>
+      </c>
+      <c r="D225" t="s">
+        <v>968</v>
+      </c>
+      <c r="E225" t="s">
+        <v>971</v>
+      </c>
+      <c r="G225" t="s">
+        <v>958</v>
+      </c>
+      <c r="H225" t="s">
+        <v>959</v>
+      </c>
+      <c r="I225">
+        <v>2023</v>
+      </c>
+      <c r="L225" t="s">
+        <v>873</v>
+      </c>
+      <c r="M225" t="s">
+        <v>873</v>
+      </c>
+      <c r="N225" t="s">
+        <v>874</v>
+      </c>
+      <c r="O225" t="s">
+        <v>960</v>
+      </c>
+      <c r="P225" t="s">
+        <v>224</v>
+      </c>
+      <c r="V225" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z225" s="6" t="s">
+        <v>972</v>
+      </c>
+      <c r="AA225" s="7" t="s">
+        <v>976</v>
+      </c>
+      <c r="AB225" s="4">
+        <v>1958.5</v>
+      </c>
+      <c r="AC225" s="8">
+        <v>54.8</v>
+      </c>
+      <c r="AD225" s="8">
+        <v>9.2200000000000006</v>
+      </c>
+      <c r="AE225" s="8">
+        <v>0.26100000000000001</v>
+      </c>
+      <c r="AF225" s="8">
+        <v>-48.7</v>
+      </c>
+      <c r="AG225" s="8">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="AH225" s="8">
+        <v>0.27</v>
+      </c>
+      <c r="AI225" s="8">
+        <v>130</v>
+      </c>
+      <c r="AJ225" s="8">
+        <v>1.26E-2</v>
+      </c>
+      <c r="AK225" s="8">
+        <v>210</v>
+      </c>
+      <c r="AL225" s="9"/>
+      <c r="AM225" s="8">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="AN225" s="8">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="AS225" s="11" t="s">
+        <v>979</v>
+      </c>
+      <c r="AU225" s="8">
+        <v>0.104</v>
+      </c>
+      <c r="AV225" s="11" t="s">
+        <v>984</v>
+      </c>
+      <c r="AX225" s="10">
+        <v>0.22700000000000001</v>
+      </c>
+      <c r="AY225" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="BA225" s="11" t="s">
+        <v>988</v>
+      </c>
+      <c r="BC225" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="BF225" s="6" t="s">
+        <v>992</v>
+      </c>
+      <c r="BI225" s="6" t="s">
+        <v>997</v>
+      </c>
+      <c r="BK225">
+        <v>0.87366699999999997</v>
+      </c>
+      <c r="BL225" s="6" t="s">
+        <v>999</v>
+      </c>
+      <c r="BM225" s="6" t="s">
+        <v>1000</v>
+      </c>
+      <c r="BP225" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="BS225" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="BT225" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="BU225" s="6" t="s">
+        <v>1005</v>
+      </c>
+      <c r="BX225">
+        <v>0.71033299999999999</v>
+      </c>
+      <c r="CB225" s="6" t="s">
+        <v>1006</v>
+      </c>
+      <c r="CC225" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="GP225" s="6" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="226" spans="1:198" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A226" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B226" t="s">
+        <v>954</v>
+      </c>
+      <c r="C226" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D226" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E226" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G226" t="s">
+        <v>958</v>
+      </c>
+      <c r="H226" t="s">
+        <v>959</v>
+      </c>
+      <c r="I226">
+        <v>2023</v>
+      </c>
+      <c r="L226" t="s">
+        <v>873</v>
+      </c>
+      <c r="M226" t="s">
+        <v>873</v>
+      </c>
+      <c r="N226" t="s">
+        <v>874</v>
+      </c>
+      <c r="O226" t="s">
+        <v>960</v>
+      </c>
+      <c r="P226" t="s">
+        <v>224</v>
+      </c>
+      <c r="V226" t="s">
+        <v>329</v>
+      </c>
+      <c r="Z226" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="AA226" s="11" t="s">
+        <v>1013</v>
+      </c>
+      <c r="AB226" s="8">
+        <v>1637</v>
+      </c>
+      <c r="AC226" s="8">
+        <v>44.6</v>
+      </c>
+      <c r="AD226" s="8">
+        <v>9.4</v>
+      </c>
+      <c r="AE226" s="8">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="AF226" s="8">
+        <v>-45</v>
+      </c>
+      <c r="AG226" s="8">
+        <v>13.7</v>
+      </c>
+      <c r="AH226" s="8">
+        <v>0.82</v>
+      </c>
+      <c r="AI226" s="8">
+        <v>180</v>
+      </c>
+      <c r="AJ226" s="8">
+        <v>1.7500000000000002E-2</v>
+      </c>
+      <c r="AK226" s="8">
+        <v>197.99</v>
+      </c>
+      <c r="AM226" s="8">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="AN226" s="8">
+        <v>0.03</v>
+      </c>
+      <c r="AS226" s="12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="AT226" s="9"/>
+      <c r="AU226" s="8">
+        <v>0.1095</v>
+      </c>
+      <c r="AV226" s="11" t="s">
+        <v>1015</v>
+      </c>
+      <c r="AW226" s="9"/>
+      <c r="AX226" s="8">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="AY226" s="11" t="s">
+        <v>1016</v>
+      </c>
+      <c r="AZ226" s="8">
+        <v>0.124</v>
+      </c>
+      <c r="BA226" s="11" t="s">
+        <v>1017</v>
+      </c>
+      <c r="BB226" s="9"/>
+      <c r="BC226" s="11" t="s">
+        <v>1018</v>
+      </c>
+      <c r="GP226" s="6" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="227" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A227" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C227" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H227" t="s">
+        <v>1026</v>
+      </c>
+      <c r="O227" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z227" s="13">
+        <v>27.006471269999999</v>
+      </c>
+      <c r="AA227" s="13">
+        <v>-111.40934841000001</v>
+      </c>
+      <c r="AB227">
+        <v>-2005</v>
+      </c>
+      <c r="AC227" s="14">
+        <v>35</v>
+      </c>
+      <c r="GP227" s="6" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="228" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A228" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C228" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H228" t="s">
+        <v>1026</v>
+      </c>
+      <c r="O228" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z228" s="13">
+        <v>27.006471269999999</v>
+      </c>
+      <c r="AA228" s="13">
+        <v>-111.40934841000001</v>
+      </c>
+      <c r="AB228">
+        <v>-2005</v>
+      </c>
+      <c r="AC228" s="14">
+        <v>32</v>
+      </c>
+      <c r="GP228" s="6" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="229" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A229" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C229" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H229" t="s">
+        <v>1026</v>
+      </c>
+      <c r="O229" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z229" s="13">
+        <v>27.006471269999999</v>
+      </c>
+      <c r="AA229" s="13">
+        <v>-111.40934841000001</v>
+      </c>
+      <c r="AB229">
+        <v>-2005</v>
+      </c>
+      <c r="AC229" s="14">
+        <v>46</v>
+      </c>
+      <c r="GP229" s="6" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="230" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A230" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C230" t="s">
+        <v>662</v>
+      </c>
+      <c r="H230" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O230" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z230" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AA230" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AB230">
+        <v>-2503</v>
+      </c>
+      <c r="AC230" s="14">
+        <v>29.2</v>
+      </c>
+      <c r="AD230">
+        <v>7.5</v>
+      </c>
+      <c r="GP230" s="6" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="231" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A231" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C231" t="s">
+        <v>662</v>
+      </c>
+      <c r="H231" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O231" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z231" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AA231" t="s">
+        <v>1038</v>
+      </c>
+      <c r="AB231">
+        <v>-2511</v>
+      </c>
+      <c r="AC231" s="14">
+        <v>14.5</v>
+      </c>
+      <c r="AD231">
+        <v>6.3</v>
+      </c>
+      <c r="GP231" s="6" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="232" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A232" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C232" t="s">
+        <v>662</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O232" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z232" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AA232" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AB232">
+        <v>-2503</v>
+      </c>
+      <c r="AC232" s="14">
+        <v>15.4</v>
+      </c>
+      <c r="AD232">
+        <v>6.8</v>
+      </c>
+      <c r="GP232" s="6" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="233" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A233" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C233" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H233" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O233" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z233" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="AA233" t="s">
+        <v>1040</v>
+      </c>
+      <c r="AB233">
+        <v>-2503</v>
+      </c>
+      <c r="AC233" s="14">
+        <v>5.7</v>
+      </c>
+      <c r="AD233">
+        <v>6.7</v>
+      </c>
+      <c r="GP233" s="6" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="234" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A234" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C234" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H234" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O234" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z234" s="6" t="s">
+        <v>1034</v>
+      </c>
+      <c r="AA234" t="s">
+        <v>1035</v>
+      </c>
+      <c r="AB234">
+        <v>-2503</v>
+      </c>
+      <c r="AC234" s="14">
+        <v>29.2</v>
+      </c>
+      <c r="AD234">
+        <v>7.5</v>
+      </c>
+      <c r="GP234" s="6" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="235" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A235" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C235" t="s">
+        <v>662</v>
+      </c>
+      <c r="H235" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O235" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z235" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AA235" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AB235">
+        <v>-2514</v>
+      </c>
+      <c r="AC235" s="14">
+        <v>4.7</v>
+      </c>
+      <c r="AD235">
+        <v>7.2</v>
+      </c>
+      <c r="GP235" s="6" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="236" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A236" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C236" t="s">
+        <v>662</v>
+      </c>
+      <c r="H236" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O236" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z236" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="AA236" t="s">
+        <v>1055</v>
+      </c>
+      <c r="AB236">
+        <v>-2507</v>
+      </c>
+      <c r="AC236" s="14">
+        <v>8</v>
+      </c>
+      <c r="AD236">
+        <v>6.7</v>
+      </c>
+      <c r="GP236" s="6" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="237" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A237" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C237" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H237" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O237" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z237" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="AA237" t="s">
+        <v>1060</v>
+      </c>
+      <c r="AB237">
+        <v>-2506</v>
+      </c>
+      <c r="AC237" s="14">
+        <v>6.6</v>
+      </c>
+      <c r="AD237">
+        <v>7</v>
+      </c>
+      <c r="GP237" s="6" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="238" spans="1:198" x14ac:dyDescent="0.3">
+      <c r="A238" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C238" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H238" t="s">
+        <v>1033</v>
+      </c>
+      <c r="O238" t="s">
+        <v>904</v>
+      </c>
+      <c r="Z238" s="6" t="s">
+        <v>1050</v>
+      </c>
+      <c r="AA238" t="s">
+        <v>1051</v>
+      </c>
+      <c r="AB238">
+        <v>-2514</v>
+      </c>
+      <c r="AC238" s="14">
+        <v>6.1</v>
+      </c>
+      <c r="AD238">
+        <v>7</v>
+      </c>
+      <c r="GP238" s="6" t="s">
+        <v>1052</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>